--- a/data/4-reports/7_SNOMED_Matches_All.xlsx
+++ b/data/4-reports/7_SNOMED_Matches_All.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K216"/>
+  <dimension ref="A1:K212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4729,22 +4729,22 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Eosinophilic Esophagitis</t>
+          <t>Epilepsy</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>235599003</t>
+          <t>84757009</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Eosinophilic esophagitis</t>
+          <t>Epilepsy</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -4759,13 +4759,13 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>27918</t>
+          <t>380378</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>235599003</t>
+          <t>84757009</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Epilepsy</t>
+          <t>Episcleritis</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>84757009</t>
+          <t>815008</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Epilepsy</t>
+          <t>Episcleritis</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4812,13 +4812,13 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>380378</t>
+          <t>4218083</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>84757009</t>
+          <t>815008</t>
         </is>
       </c>
       <c r="K89" s="5" t="inlineStr">
@@ -4835,17 +4835,17 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Episcleritis</t>
+          <t>Erythema nodosum</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>815008</t>
+          <t>32861005</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Episcleritis</t>
+          <t>Erythema nodosum</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4865,13 +4865,13 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>4218083</t>
+          <t>140176</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>815008</t>
+          <t>32861005</t>
         </is>
       </c>
       <c r="K90" s="5" t="inlineStr">
@@ -4888,17 +4888,17 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Erythema nodosum</t>
+          <t>Essential mixed cryoglobulinemia</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>32861005</t>
+          <t>239947001</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Erythema nodosum</t>
+          <t>Essential mixed cryoglobulinemia</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4918,13 +4918,13 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>140176</t>
+          <t>4347067</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>32861005</t>
+          <t>239947001</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
@@ -4941,17 +4941,17 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Essential mixed cryoglobulinemia</t>
+          <t>Evans syndrome</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>239947001</t>
+          <t>75331009</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Essential mixed cryoglobulinemia</t>
+          <t>Evans syndrome</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4971,13 +4971,13 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>4347067</t>
+          <t>436956</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>239947001</t>
+          <t>75331009</t>
         </is>
       </c>
       <c r="K92" s="5" t="inlineStr">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Evans syndrome</t>
+          <t>Fasciitis with eosinophilia syndrome</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>75331009</t>
+          <t>24129002</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Evans syndrome</t>
+          <t>Fasciitis with eosinophilia syndrome</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5024,13 +5024,13 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>436956</t>
+          <t>4083100</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>75331009</t>
+          <t>24129002</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
@@ -5047,17 +5047,17 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Fasciitis with eosinophilia syndrome</t>
+          <t>Felty syndrome</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>24129002</t>
+          <t>57160007</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Fasciitis with eosinophilia syndrome</t>
+          <t>Felty's syndrome</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5072,18 +5072,18 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Felty's syndrome</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>4083100</t>
+          <t>81097</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>24129002</t>
+          <t>57160007</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Felty syndrome</t>
+          <t>Female infertility due to antisperm antibodies</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>57160007</t>
+          <t>414238007</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Felty's syndrome</t>
+          <t>Female infertility due to antisperm antibody</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -5125,18 +5125,18 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Felty's syndrome</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>81097</t>
+          <t>4188008</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>57160007</t>
+          <t>414238007, 236816007</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
@@ -5153,22 +5153,22 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Female infertility due to antisperm antibodies</t>
+          <t>Fibromyalgia</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>414238007</t>
+          <t>203082005</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Female infertility due to antisperm antibody</t>
+          <t>Fibromyalgia</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -5183,13 +5183,13 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>4188008</t>
+          <t>40405599</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>414238007, 236816007</t>
+          <t>203082005</t>
         </is>
       </c>
       <c r="K96" s="5" t="inlineStr">
@@ -5206,17 +5206,17 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Fibromyalgia</t>
+          <t>Graves' disease</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>203082005</t>
+          <t>353295004</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Fibromyalgia</t>
+          <t>Graves' disease</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5236,13 +5236,13 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>40405599</t>
+          <t>4232076</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>203082005</t>
+          <t>353295004, 90739004, 237499004</t>
         </is>
       </c>
       <c r="K97" s="5" t="inlineStr">
@@ -5259,17 +5259,17 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Graves' disease</t>
+          <t>Guillain-Barré syndrome</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>353295004</t>
+          <t>40956001</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Graves' disease</t>
+          <t>Guillain-Barré syndrome</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5289,13 +5289,13 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>4232076</t>
+          <t>4164770</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>353295004, 90739004, 237499004</t>
+          <t>715770009, 1767005, 40956001, 716723000</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Guillain-Barré syndrome</t>
+          <t>Hemophilia B Leyden</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>40956001</t>
+          <t>1336117005</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Guillain-Barré syndrome</t>
+          <t>Hemophilia B Leyden</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5342,13 +5342,13 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>4164770</t>
+          <t>1076202</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>715770009, 1767005, 40956001, 716723000</t>
+          <t>1336117005</t>
         </is>
       </c>
       <c r="K99" s="5" t="inlineStr">
@@ -5365,17 +5365,17 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Hemophilia B Leyden</t>
+          <t>Herpes gestationis</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>1336117005</t>
+          <t>86081009</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Hemophilia B Leyden</t>
+          <t>Herpes gestationis</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5395,13 +5395,13 @@
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>1076202</t>
+          <t>4311256</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>1336117005</t>
+          <t>86081009</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
@@ -5418,17 +5418,17 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Herpes gestationis</t>
+          <t>Hidradenitis suppurativa</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>86081009</t>
+          <t>59393003</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Herpes gestationis</t>
+          <t>Hidradenitis suppurativa</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5448,13 +5448,13 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>4311256</t>
+          <t>4241223</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>86081009</t>
+          <t>59393003</t>
         </is>
       </c>
       <c r="K101" s="5" t="inlineStr">
@@ -5471,17 +5471,17 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Hidradenitis suppurativa</t>
+          <t>Hypersensitivity angiitis</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>59393003</t>
+          <t>60555002</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Hidradenitis suppurativa</t>
+          <t>Hypersensitivity angiitis</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5501,13 +5501,13 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>4241223</t>
+          <t>196431</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>59393003</t>
+          <t>60555002</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
@@ -5524,17 +5524,17 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Hypersensitivity angiitis</t>
+          <t>Idiopathic membranous glomerulonephritis</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>60555002</t>
+          <t>722119002</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Hypersensitivity angiitis</t>
+          <t>Idiopathic membranous glomerulonephritis</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5554,13 +5554,13 @@
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>196431</t>
+          <t>36716199</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>60555002</t>
+          <t>722119002</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr">
@@ -5577,17 +5577,17 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Idiopathic membranous glomerulonephritis</t>
+          <t>Idiopathic pulmonary fibrosis</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>722119002</t>
+          <t>700250006</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Idiopathic membranous glomerulonephritis</t>
+          <t>Idiopathic pulmonary fibrosis</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5607,13 +5607,13 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>36716199</t>
+          <t>45763750</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>722119002</t>
+          <t>700250006</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr">
@@ -5630,17 +5630,17 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Idiopathic pulmonary fibrosis</t>
+          <t>IgA nephropathy</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>700250006</t>
+          <t>236407003</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Idiopathic pulmonary fibrosis</t>
+          <t>IgA nephropathy</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5660,13 +5660,13 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>45763750</t>
+          <t>4128061</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>700250006</t>
+          <t>236407003</t>
         </is>
       </c>
       <c r="K105" s="5" t="inlineStr">
@@ -5683,50 +5683,22 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>IgA nephropathy</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>236407003</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>IgA nephropathy</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Immune checkpoint inhibitor-induced autoimmunity</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr"/>
+      <c r="D106" s="3" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>4128061</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>236407003</t>
-        </is>
-      </c>
-      <c r="K106" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J106" s="3" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -5736,7 +5708,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Immune checkpoint inhibitor-induced autoimmunity</t>
+          <t>Immune Dysregulation, Polyendocrinopathy, Enteropathy, X-Linked Syndrome</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr"/>
@@ -5761,22 +5733,50 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Immune Dysregulation, Polyendocrinopathy, Enteropathy, X-Linked Syndrome</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr"/>
-      <c r="D108" s="3" t="inlineStr"/>
-      <c r="E108" s="2" t="inlineStr"/>
-      <c r="F108" s="2" t="inlineStr"/>
+          <t>Immune thrombocytopenia</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>2897005</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Immune thrombocytopenia</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>4103532</t>
+        </is>
+      </c>
       <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="3" t="inlineStr"/>
-      <c r="K108" s="2" t="inlineStr"/>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>13172003, 128092005, 2897005, 438476003, 32273002, 128091003</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -5786,17 +5786,17 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Immune thrombocytopenia</t>
+          <t>Immunoglobulin A vasculitis</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>2897005</t>
+          <t>191306005</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Immune thrombocytopenia</t>
+          <t>Immunoglobulin A vasculitis</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5816,13 +5816,13 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>4103532</t>
+          <t>4101602</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>13172003, 128092005, 2897005, 438476003, 32273002, 128091003</t>
+          <t>191306005</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr">
@@ -5839,17 +5839,17 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin A vasculitis</t>
+          <t>Immunoglobulin G4 related disease</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>191306005</t>
+          <t>10743271000119103</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin A vasculitis</t>
+          <t>Immunoglobulin G4 related disease</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5869,13 +5869,13 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>4101602</t>
+          <t>36717255</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>191306005</t>
+          <t>10743271000119103, 234549008, 722870008</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
@@ -5892,17 +5892,17 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin G4 related disease</t>
+          <t>Immunoglobulin G4 related ophthalmic disease</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>10743271000119103</t>
+          <t>1187510006</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin G4 related disease</t>
+          <t>Immunoglobulin G4 related ophthalmic disease</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5922,13 +5922,13 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>36717255</t>
+          <t>37162346</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>10743271000119103, 234549008, 722870008</t>
+          <t>1187510006</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr">
@@ -5945,17 +5945,17 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin G4 related ophthalmic disease</t>
+          <t>Inclusion body myositis</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>1187510006</t>
+          <t>72315009</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin G4 related ophthalmic disease</t>
+          <t>Inclusion body myositis</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -5975,13 +5975,13 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>37162346</t>
+          <t>4216406</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>1187510006</t>
+          <t>72315009</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
@@ -5998,17 +5998,17 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Inclusion Body Myositis</t>
+          <t>Inflammatory Bowel Disease</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>72315009</t>
+          <t>24526004</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Inclusion body myositis</t>
+          <t>Inflammatory bowel disease</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6028,13 +6028,13 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>4216406</t>
+          <t>4074815</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>72315009</t>
+          <t>24526004</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
@@ -6051,17 +6051,17 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Inclusion body myositis</t>
+          <t>Insulin autoimmune syndrome</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>72315009</t>
+          <t>408539000</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Inclusion body myositis</t>
+          <t>Insulin autoimmune syndrome</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6081,13 +6081,13 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>4216406</t>
+          <t>4252384</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>72315009</t>
+          <t>408539000</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
@@ -6104,22 +6104,22 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Inflammatory Bowel Disease</t>
+          <t>Insulin resistance - type B</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>24526004</t>
+          <t>237652003</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Inflammatory bowel disease</t>
+          <t>Insulin resistance - type B</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -6134,13 +6134,13 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>4074815</t>
+          <t>4129525</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>24526004</t>
+          <t>237652003</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr">
@@ -6157,17 +6157,17 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Insulin autoimmune syndrome</t>
+          <t>Intermediate uveitis</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>408539000</t>
+          <t>314429009</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Insulin autoimmune syndrome</t>
+          <t>Intermediate uveitis</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6187,13 +6187,13 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>4252384</t>
+          <t>4197155</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>408539000</t>
+          <t>314429009, 1231232007, 45688009</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
@@ -6210,17 +6210,17 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Insulin resistance - type B</t>
+          <t>Interstitial lung disease</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>237652003</t>
+          <t>233703007</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Insulin resistance - type B</t>
+          <t>Interstitial lung disease</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6240,13 +6240,13 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>4129525</t>
+          <t>4119786</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>237652003</t>
+          <t>233703007</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
@@ -6263,17 +6263,17 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Intermediate uveitis</t>
+          <t>Juvenile Rheumatoid Arthritis</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>314429009</t>
+          <t>410502007</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Intermediate uveitis</t>
+          <t>Juvenile idiopathic arthritis</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6288,25 +6288,21 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Juvenile idiopathic arthritis</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>4197155</t>
+          <t>4259507</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>314429009, 1231232007, 45688009</t>
-        </is>
-      </c>
-      <c r="K118" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>410795001, 239796000</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -6316,17 +6312,17 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Interstitial lung disease</t>
+          <t>Lichen planus</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>233703007</t>
+          <t>4776004</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Interstitial lung disease</t>
+          <t>Lichen planus</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6346,13 +6342,13 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>4119786</t>
+          <t>132703</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>233703007</t>
+          <t>4776004</t>
         </is>
       </c>
       <c r="K119" s="5" t="inlineStr">
@@ -6369,17 +6365,17 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Juvenile Rheumatoid Arthritis</t>
+          <t>Lichen sclerosus</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>410502007</t>
+          <t>895454001</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Juvenile idiopathic arthritis</t>
+          <t>Lichen sclerosus</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6394,21 +6390,25 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>Juvenile idiopathic arthritis</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>4259507</t>
+          <t>619430</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>410795001, 239796000</t>
-        </is>
-      </c>
-      <c r="K120" s="2" t="inlineStr"/>
+          <t>895454001, 25674000</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -6418,17 +6418,17 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Lichen planus</t>
+          <t>Ligneous conjunctivitis</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>4776004</t>
+          <t>403435005</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Lichen planus</t>
+          <t>Ligneous conjunctivitis</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6448,13 +6448,13 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>132703</t>
+          <t>4296491</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>4776004</t>
+          <t>403435005</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr">
@@ -6471,17 +6471,17 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Lichen sclerosus</t>
+          <t>Limbic encephalitis</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>895454001</t>
+          <t>230192003</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Lichen sclerosus</t>
+          <t>Limbic encephalitis</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6501,13 +6501,13 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>619430</t>
+          <t>4041673</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>895454001, 25674000</t>
+          <t>230192003</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
@@ -6524,17 +6524,17 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Ligneous conjunctivitis</t>
+          <t>Limbic encephalitis with dipeptidyl-peptidase 6 antibodies</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>403435005</t>
+          <t>773395008</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Ligneous conjunctivitis</t>
+          <t>Limbic encephalitis with dipeptidyl-peptidase 6 antibodies</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6554,13 +6554,13 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>4296491</t>
+          <t>36676495</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>403435005</t>
+          <t>773395008</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
@@ -6577,17 +6577,17 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis</t>
+          <t>Limbic encephalitis with leucine-rich glioma-inactivated 1 antibodies</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>230192003</t>
+          <t>763794005</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis</t>
+          <t>Limbic encephalitis with leucine-rich glioma-inactivated 1 antibodies</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6607,13 +6607,13 @@
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>4041673</t>
+          <t>35607961</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>230192003</t>
+          <t>763794005</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
@@ -6630,17 +6630,17 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis with dipeptidyl-peptidase 6 antibodies</t>
+          <t>Linear IgA dermatosis</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>773395008</t>
+          <t>95330001</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis with dipeptidyl-peptidase 6 antibodies</t>
+          <t>Linear IgA dermatosis</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6660,13 +6660,13 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>36676495</t>
+          <t>4317262</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>773395008</t>
+          <t>95330001</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr">
@@ -6683,17 +6683,17 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis with leucine-rich glioma-inactivated 1 antibodies</t>
+          <t>Lipomatosis dolorosa</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>763794005</t>
+          <t>71404003</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis with leucine-rich glioma-inactivated 1 antibodies</t>
+          <t>Lipomatosis dolorosa</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6713,13 +6713,13 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>35607961</t>
+          <t>4324974</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>763794005</t>
+          <t>71404003</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
@@ -6736,17 +6736,17 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Linear IgA dermatosis</t>
+          <t>Lupus vasculitis</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>95330001</t>
+          <t>239944008</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Linear IgA dermatosis</t>
+          <t>Lupus vasculitis</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -6766,13 +6766,13 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>4317262</t>
+          <t>4344495</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>95330001</t>
+          <t>239944008</t>
         </is>
       </c>
       <c r="K127" s="5" t="inlineStr">
@@ -6789,50 +6789,26 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Lipomatosis dolorosa</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>71404003</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>Lipomatosis dolorosa</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Male infertility associated with antisperm antibodies</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr"/>
+      <c r="D128" s="3" t="inlineStr"/>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr">
-        <is>
-          <t>4324974</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr"/>
       <c r="I128" s="2" t="inlineStr"/>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>71404003</t>
-        </is>
-      </c>
-      <c r="K128" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>414643008</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -6842,17 +6818,17 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Lupus vasculitis</t>
+          <t>Microscopic colitis</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>239944008</t>
+          <t>235753003</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Lupus vasculitis</t>
+          <t>Microscopic colitis</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6872,13 +6848,13 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>4344495</t>
+          <t>4340799</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>239944008</t>
+          <t>235753003</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr">
@@ -6895,26 +6871,50 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Male infertility associated with antisperm antibodies</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr"/>
-      <c r="D130" s="3" t="inlineStr"/>
-      <c r="E130" s="2" t="inlineStr"/>
-      <c r="F130" s="2" t="inlineStr"/>
+          <t>Microscopic polyangiitis</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>1144805008</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Microscopic polyangiitis</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>606328</t>
+        </is>
+      </c>
       <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>414643008</t>
-        </is>
-      </c>
-      <c r="K130" s="2" t="inlineStr"/>
+          <t>1144805008</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -6924,17 +6924,17 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Microscopic colitis</t>
+          <t>Mixed collagen vascular disease</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>235753003</t>
+          <t>398049005</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Microscopic colitis</t>
+          <t>Mixed collagen vascular disease</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -6954,13 +6954,13 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>4340799</t>
+          <t>4134867</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>235753003</t>
+          <t>398049005</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr">
@@ -6977,17 +6977,17 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Microscopic polyangiitis</t>
+          <t>Mooren's ulcer</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>1144805008</t>
+          <t>22440001</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Microscopic polyangiitis</t>
+          <t>Mooren's ulcer</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7007,13 +7007,13 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>606328</t>
+          <t>435271</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>1144805008</t>
+          <t>22440001</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
@@ -7030,17 +7030,17 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Mixed collagen vascular disease</t>
+          <t>Morphea</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>398049005</t>
+          <t>201049004</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Mixed collagen vascular disease</t>
+          <t>Morphea</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7060,13 +7060,13 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>4134867</t>
+          <t>4066845</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>398049005</t>
+          <t>201048007, 201049004</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr">
@@ -7083,17 +7083,17 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Mooren's ulcer</t>
+          <t>Motor neuropathy with multiple conduction block</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>22440001</t>
+          <t>230591002</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Mooren's ulcer</t>
+          <t>Motor neuropathy with multiple conduction block</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7113,13 +7113,13 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>435271</t>
+          <t>4046338</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>22440001</t>
+          <t>230591002</t>
         </is>
       </c>
       <c r="K134" s="5" t="inlineStr">
@@ -7136,17 +7136,17 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Morphea</t>
+          <t>Moyamoya disease</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>201049004</t>
+          <t>69116000</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Morphea</t>
+          <t>Moyamoya disease</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7166,13 +7166,13 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>4066845</t>
+          <t>378774</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>201048007, 201049004</t>
+          <t>69116000</t>
         </is>
       </c>
       <c r="K135" s="5" t="inlineStr">
@@ -7189,17 +7189,17 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Motor neuropathy with multiple conduction block</t>
+          <t>Multiple sclerosis</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>230591002</t>
+          <t>24700007</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Motor neuropathy with multiple conduction block</t>
+          <t>Multiple sclerosis</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7219,13 +7219,13 @@
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>4046338</t>
+          <t>374919</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>230591002</t>
+          <t>24700007, 428700003, 426373005, 49692006, 128460000</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr">
@@ -7242,17 +7242,17 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Moyamoya disease</t>
+          <t>Myasthenia gravis</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>69116000</t>
+          <t>91637004</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Moyamoya disease</t>
+          <t>Myasthenia gravis</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7272,13 +7272,13 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>378774</t>
+          <t>76685</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr"/>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>69116000</t>
+          <t>91637004</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
@@ -7295,17 +7295,17 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Multiple sclerosis</t>
+          <t>Myelin oligodendrocyte glycoprotein antibody-associated disease</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>24700007</t>
+          <t>1237194006</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Multiple sclerosis</t>
+          <t>Myelin oligodendrocyte glycoprotein antibody-associated disease</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7325,13 +7325,13 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>374919</t>
+          <t>37164973</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>24700007, 428700003, 426373005, 49692006, 128460000</t>
+          <t>1237194006, 718213001</t>
         </is>
       </c>
       <c r="K138" s="5" t="inlineStr">
@@ -7348,22 +7348,22 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Multiple Sclerosis</t>
+          <t>Myocarditis due to autoimmune disease</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>24700007</t>
+          <t>871640001</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Multiple sclerosis</t>
+          <t>Myocarditis due to autoimmune disease</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -7378,13 +7378,13 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>374919</t>
+          <t>3656114</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>24700007</t>
+          <t>871640001, 37217002</t>
         </is>
       </c>
       <c r="K139" s="5" t="inlineStr">
@@ -7401,17 +7401,17 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Myasthenia gravis</t>
+          <t>Myositis</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>91637004</t>
+          <t>26889001</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Myasthenia gravis</t>
+          <t>Myositis</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7431,13 +7431,13 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>76685</t>
+          <t>73001</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>91637004</t>
+          <t>722991004, 715863001, 702380008, 26889001</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Myelin oligodendrocyte glycoprotein antibody-associated disease</t>
+          <t>Necrotizing vasculitis</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>1237194006</t>
+          <t>11791001</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Myelin oligodendrocyte glycoprotein antibody-associated disease</t>
+          <t>Necrotizing vasculitis</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7484,13 +7484,13 @@
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>37164973</t>
+          <t>4039691</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>1237194006, 718213001</t>
+          <t>11791001</t>
         </is>
       </c>
       <c r="K141" s="5" t="inlineStr">
@@ -7507,17 +7507,17 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Myocarditis due to autoimmune disease</t>
+          <t>Neonatal lupus erythematosus</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>871640001</t>
+          <t>95609003</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Myocarditis due to autoimmune disease</t>
+          <t>Neonatal lupus erythematosus</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7537,13 +7537,13 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>3656114</t>
+          <t>4316373</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>871640001, 37217002</t>
+          <t>95609003</t>
         </is>
       </c>
       <c r="K142" s="5" t="inlineStr">
@@ -7560,17 +7560,17 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Myositis</t>
+          <t>Neuralgic amyotrophy</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>26889001</t>
+          <t>26609002</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Myositis</t>
+          <t>Neuralgic amyotrophy</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7590,13 +7590,13 @@
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>377271</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>722991004, 715863001, 702380008, 26889001</t>
+          <t>3548001, 26609002</t>
         </is>
       </c>
       <c r="K143" s="5" t="inlineStr">
@@ -7613,17 +7613,17 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Necrotizing vasculitis</t>
+          <t>Neuromyelitis optica</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>11791001</t>
+          <t>25044007</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Necrotizing vasculitis</t>
+          <t>Neuromyelitis optica</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7643,13 +7643,13 @@
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>4039691</t>
+          <t>380995</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>11791001</t>
+          <t>25044007</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr">
@@ -7666,17 +7666,17 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Neonatal lupus erythematosus</t>
+          <t>Neuromyotonia</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>95609003</t>
+          <t>305719002</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Neonatal lupus erythematosus</t>
+          <t>Neuromyotonia</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -7696,13 +7696,13 @@
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>4316373</t>
+          <t>4125693</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr"/>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>95609003</t>
+          <t>305719002</t>
         </is>
       </c>
       <c r="K145" s="5" t="inlineStr">
@@ -7719,50 +7719,26 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Neuralgic amyotrophy</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>26609002</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>Neuralgic amyotrophy</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Ocular myasthenia gravis</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr"/>
+      <c r="D146" s="3" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr">
-        <is>
-          <t>377271</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr"/>
       <c r="I146" s="2" t="inlineStr"/>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>3548001, 26609002</t>
-        </is>
-      </c>
-      <c r="K146" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>230684008</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -7772,17 +7748,17 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Neuromyelitis optica</t>
+          <t>Ophthalmoplegia due to Graves' disease</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>25044007</t>
+          <t>104461000119104</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Neuromyelitis optica</t>
+          <t>Ophthalmoplegia due to Graves' disease</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -7802,13 +7778,13 @@
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>380995</t>
+          <t>45757069</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr"/>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>25044007</t>
+          <t>104461000119104, 276177000</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
@@ -7825,17 +7801,17 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Neuromyotonia</t>
+          <t>Opsoclonus-myoclonus syndrome</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>305719002</t>
+          <t>230350000</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Neuromyotonia</t>
+          <t>Opsoclonus-myoclonus syndrome</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -7855,13 +7831,13 @@
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>4125693</t>
+          <t>4043399</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>305719002</t>
+          <t>230350000</t>
         </is>
       </c>
       <c r="K148" s="5" t="inlineStr">
@@ -7878,26 +7854,50 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Ocular myasthenia gravis</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr"/>
-      <c r="D149" s="3" t="inlineStr"/>
-      <c r="E149" s="2" t="inlineStr"/>
-      <c r="F149" s="2" t="inlineStr"/>
+          <t>Palindromic rheumatism</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>50442003</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Palindromic rheumatism</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>76196</t>
+        </is>
+      </c>
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>230684008</t>
-        </is>
-      </c>
-      <c r="K149" s="2" t="inlineStr"/>
+          <t>50442003</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -7907,17 +7907,17 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Ophthalmoplegia due to Graves' disease</t>
+          <t>Paraneoplastic cerebellar degeneration</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>104461000119104</t>
+          <t>192877007</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Ophthalmoplegia due to Graves' disease</t>
+          <t>Paraneoplastic cerebellar degeneration</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -7937,13 +7937,13 @@
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>45757069</t>
+          <t>4102330</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr"/>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>104461000119104, 276177000</t>
+          <t>192877007</t>
         </is>
       </c>
       <c r="K150" s="5" t="inlineStr">
@@ -7960,50 +7960,22 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Opsoclonus-myoclonus syndrome</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>230350000</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>Opsoclonus-myoclonus syndrome</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Paraneoplastic pemphigus</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr"/>
+      <c r="D151" s="3" t="inlineStr"/>
+      <c r="E151" s="2" t="inlineStr"/>
+      <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H151" s="4" t="inlineStr">
-        <is>
-          <t>4043399</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr"/>
       <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>230350000</t>
-        </is>
-      </c>
-      <c r="K151" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J151" s="3" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -8013,17 +7985,17 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Palindromic rheumatism</t>
+          <t>Paroxysmal cold hemoglobinuria</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>50442003</t>
+          <t>127057004</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Palindromic rheumatism</t>
+          <t>Paroxysmal cold hemoglobinuria</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8043,13 +8015,13 @@
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>76196</t>
+          <t>4131917</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr"/>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>50442003</t>
+          <t>127057004</t>
         </is>
       </c>
       <c r="K152" s="5" t="inlineStr">
@@ -8066,17 +8038,17 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Paraneoplastic cerebellar degeneration</t>
+          <t>Paroxysmal nocturnal hemoglobinuria</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>192877007</t>
+          <t>1963002</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Paraneoplastic cerebellar degeneration</t>
+          <t>Paroxysmal nocturnal hemoglobinuria</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8096,13 +8068,13 @@
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>4102330</t>
+          <t>4024671</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr"/>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>192877007</t>
+          <t>1963002</t>
         </is>
       </c>
       <c r="K153" s="5" t="inlineStr">
@@ -8119,22 +8091,50 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Paraneoplastic pemphigus</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr"/>
-      <c r="D154" s="3" t="inlineStr"/>
-      <c r="E154" s="2" t="inlineStr"/>
-      <c r="F154" s="2" t="inlineStr"/>
+          <t>Pediatric autoimmune neuropsychiatric disorder associated with streptococcal infection</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>446682003</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Pediatric autoimmune neuropsychiatric disorder associated with streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>40488855</t>
+        </is>
+      </c>
       <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="3" t="inlineStr"/>
-      <c r="K154" s="2" t="inlineStr"/>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>446682003</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -8144,17 +8144,17 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Paroxysmal cold hemoglobinuria</t>
+          <t>Pemphigus</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>127057004</t>
+          <t>65172003</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Paroxysmal cold hemoglobinuria</t>
+          <t>Pemphigus</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8174,13 +8174,13 @@
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>4131917</t>
+          <t>135338</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr"/>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>127057004</t>
+          <t>46459009, 200907003, 65172003, 36739006, 35154004, 402718003, 49420001</t>
         </is>
       </c>
       <c r="K155" s="5" t="inlineStr">
@@ -8197,17 +8197,17 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Paroxysmal nocturnal hemoglobinuria</t>
+          <t>POEMS syndrome</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>1963002</t>
+          <t>79268002</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Paroxysmal nocturnal hemoglobinuria</t>
+          <t>POEMS syndrome</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8227,13 +8227,13 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>4024671</t>
+          <t>4193776</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr"/>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>1963002</t>
+          <t>79268002</t>
         </is>
       </c>
       <c r="K156" s="5" t="inlineStr">
@@ -8250,17 +8250,17 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Pediatric autoimmune neuropsychiatric disorder associated with streptococcal infection</t>
+          <t>Polyarteritis nodosa</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>446682003</t>
+          <t>155441006</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Pediatric autoimmune neuropsychiatric disorder associated with streptococcal infection</t>
+          <t>Polyarteritis nodosa</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -8280,13 +8280,13 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>40488855</t>
+          <t>320749</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr"/>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>446682003</t>
+          <t>155441006</t>
         </is>
       </c>
       <c r="K157" s="5" t="inlineStr">
@@ -8303,43 +8303,43 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Pemphigus</t>
+          <t>Polyglandular autoimmune syndrome type 1</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>65172003</t>
+          <t>11244009</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Pemphigus</t>
+          <t>Polyglandular autoimmune syndrome, type 1</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Autoimmune polyendocrinopathy-candidiasis-ectodermal dystrophy</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>135338</t>
+          <t>4008545</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>46459009, 200907003, 65172003, 36739006, 35154004, 402718003, 49420001</t>
+          <t>11244009</t>
         </is>
       </c>
       <c r="K158" s="5" t="inlineStr">
@@ -8356,50 +8356,46 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>POEMS syndrome</t>
+          <t>Polyglandular autoimmune syndrome type 2</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>79268002</t>
+          <t>403767009</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>POEMS syndrome</t>
+          <t>Acrocephalopolysyndactyly type II</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Carpenter syndrome</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>4193776</t>
+          <t>4301299</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>79268002</t>
-        </is>
-      </c>
-      <c r="K159" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>83728000</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -8409,17 +8405,17 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Polyarteritis nodosa</t>
+          <t>Polyglandular autoimmune syndrome type 3</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>155441006</t>
+          <t>449731009</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Polyarteritis nodosa</t>
+          <t>Autoimmune polyendocrine syndrome type 3</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -8434,18 +8430,18 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Autoimmune polyendocrine syndrome type 3</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>320749</t>
+          <t>42709859</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr"/>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>155441006</t>
+          <t>449731009</t>
         </is>
       </c>
       <c r="K160" s="5" t="inlineStr">
@@ -8462,43 +8458,43 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome type 1</t>
+          <t>Polyglandular autoimmune syndrome type 4</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>11244009</t>
+          <t>449730005</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome, type 1</t>
+          <t>Autoimmune polyendocrine syndrome type 4</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>name</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrinopathy-candidiasis-ectodermal dystrophy</t>
+          <t>Autoimmune polyendocrine syndrome type 4</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>4008545</t>
+          <t>42709858</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr"/>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>11244009</t>
+          <t>449730005</t>
         </is>
       </c>
       <c r="K161" s="5" t="inlineStr">
@@ -8515,46 +8511,50 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome type 2</t>
+          <t>Polymyalgia rheumatica</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>403767009</t>
+          <t>65323003</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Acrocephalopolysyndactyly type II</t>
+          <t>Polymyalgia rheumatica</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>name</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>Carpenter syndrome</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>4301299</t>
+          <t>255348</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr"/>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>83728000</t>
-        </is>
-      </c>
-      <c r="K162" s="2" t="inlineStr"/>
+          <t>65323003</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -8564,17 +8564,17 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome type 3</t>
+          <t>Polymyositis</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>449731009</t>
+          <t>31384009</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrine syndrome type 3</t>
+          <t>Polymyositis</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8589,18 +8589,18 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrine syndrome type 3</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>42709859</t>
+          <t>80800</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr"/>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>449731009</t>
+          <t>31384009</t>
         </is>
       </c>
       <c r="K163" s="5" t="inlineStr">
@@ -8617,17 +8617,17 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome type 4</t>
+          <t>Postmyocardial infarction syndrome</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>449730005</t>
+          <t>1258984009</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrine syndrome type 4</t>
+          <t>Post-cardiac injury syndrome</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8642,25 +8642,21 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrine syndrome type 4</t>
+          <t>Post-cardiac injury syndrome</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>42709858</t>
+          <t>37166030</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr"/>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>449730005</t>
-        </is>
-      </c>
-      <c r="K164" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>827164008, 66189004, 58600007, 278536002</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -8670,17 +8666,17 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Polymyalgia rheumatica</t>
+          <t>Postural orthostatic tachycardia syndrome</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>65323003</t>
+          <t>371073003</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Polymyalgia rheumatica</t>
+          <t>Postural orthostatic tachycardia syndrome</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -8700,13 +8696,13 @@
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>255348</t>
+          <t>4159659</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr"/>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>65323003</t>
+          <t>371073003</t>
         </is>
       </c>
       <c r="K165" s="5" t="inlineStr">
@@ -8723,17 +8719,17 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Polymyositis</t>
+          <t>Primary acquired chylomicronemia</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>31384009</t>
+          <t>402475008</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Polymyositis</t>
+          <t>Primary acquired chylomicronemia</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -8753,13 +8749,13 @@
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>80800</t>
+          <t>4223495</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>31384009</t>
+          <t>402475008</t>
         </is>
       </c>
       <c r="K166" s="5" t="inlineStr">
@@ -8776,17 +8772,17 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Postmyocardial infarction syndrome</t>
+          <t>Primary biliary cholangitis</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>1258984009</t>
+          <t>31712002</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Post-cardiac injury syndrome</t>
+          <t>Primary biliary cholangitis</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -8801,21 +8797,25 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>Post-cardiac injury syndrome</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>37166030</t>
+          <t>4135822</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr"/>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>827164008, 66189004, 58600007, 278536002</t>
-        </is>
-      </c>
-      <c r="K167" s="2" t="inlineStr"/>
+          <t>31712002</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -8825,17 +8825,17 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Postural orthostatic tachycardia syndrome</t>
+          <t>Primary idiopathic dilated cardiomyopathy</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>371073003</t>
+          <t>53043001</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Postural orthostatic tachycardia syndrome</t>
+          <t>Primary idiopathic dilated cardiomyopathy</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -8855,13 +8855,13 @@
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>4159659</t>
+          <t>4203149</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr"/>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>371073003</t>
+          <t>53043001</t>
         </is>
       </c>
       <c r="K168" s="5" t="inlineStr">
@@ -8878,50 +8878,26 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Primary acquired chylomicronemia</t>
-        </is>
-      </c>
-      <c r="C169" s="4" t="inlineStr">
-        <is>
-          <t>402475008</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>Primary acquired chylomicronemia</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Primary immune deficiency</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr"/>
+      <c r="D169" s="3" t="inlineStr"/>
+      <c r="E169" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H169" s="4" t="inlineStr">
-        <is>
-          <t>4223495</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr"/>
       <c r="I169" s="2" t="inlineStr"/>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>402475008</t>
-        </is>
-      </c>
-      <c r="K169" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>442459007, 362993009, 36138009, 31323000, 37548006</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -8931,17 +8907,17 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Primary biliary cholangitis</t>
+          <t>Primary sclerosing cholangitis</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>31712002</t>
+          <t>197441003</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Primary biliary cholangitis</t>
+          <t>Primary sclerosing cholangitis</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -8961,13 +8937,13 @@
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>4135822</t>
+          <t>4058821</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr"/>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>31712002</t>
+          <t>197441003</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr">
@@ -8984,17 +8960,17 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Primary idiopathic dilated cardiomyopathy</t>
+          <t>Progressive hemifacial atrophy</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>53043001</t>
+          <t>718224004</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Primary idiopathic dilated cardiomyopathy</t>
+          <t>Progressive hemifacial atrophy</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9014,13 +8990,13 @@
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>4203149</t>
+          <t>37397558</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr"/>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>53043001</t>
+          <t>718224004</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
@@ -9037,26 +9013,50 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Primary immune deficiency</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr"/>
-      <c r="D172" s="3" t="inlineStr"/>
-      <c r="E172" s="2" t="inlineStr"/>
-      <c r="F172" s="2" t="inlineStr"/>
+          <t>Psoriasis</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>9014002</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Psoriasis</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>140168</t>
+        </is>
+      </c>
       <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>442459007, 362993009, 36138009, 31323000, 37548006</t>
-        </is>
-      </c>
-      <c r="K172" s="2" t="inlineStr"/>
+          <t>37042000, 9014002</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -9066,17 +9066,17 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Primary sclerosing cholangitis</t>
+          <t>Psoriatic arthritis</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>197441003</t>
+          <t>156370009</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Primary sclerosing cholangitis</t>
+          <t>Psoriatic arthritis</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9096,13 +9096,13 @@
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>4058821</t>
+          <t>40319772</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr"/>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>197441003</t>
+          <t>156370009, 33339001</t>
         </is>
       </c>
       <c r="K173" s="5" t="inlineStr">
@@ -9119,17 +9119,17 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Progressive hemifacial atrophy</t>
+          <t>Pure red cell aplasia</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>718224004</t>
+          <t>50715003</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Progressive hemifacial atrophy</t>
+          <t>Pure red cell aplasia</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9149,13 +9149,13 @@
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>37397558</t>
+          <t>140065</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr"/>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>718224004</t>
+          <t>50715003</t>
         </is>
       </c>
       <c r="K174" s="5" t="inlineStr">
@@ -9172,17 +9172,17 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Psoriasis</t>
+          <t>Pyoderma gangrenosum</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>9014002</t>
+          <t>74578003</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Psoriasis</t>
+          <t>Pyoderma gangrenosum</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9202,13 +9202,13 @@
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>140168</t>
+          <t>133283</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr"/>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>37042000, 9014002</t>
+          <t>74578003</t>
         </is>
       </c>
       <c r="K175" s="5" t="inlineStr">
@@ -9225,17 +9225,17 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Psoriatic arthritis</t>
+          <t>Rasmussen syndrome</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>156370009</t>
+          <t>230191005</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Psoriatic arthritis</t>
+          <t>Rasmussen syndrome</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9255,13 +9255,13 @@
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>40319772</t>
+          <t>4041672</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr"/>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>156370009, 33339001</t>
+          <t>230191005, 435341000124104</t>
         </is>
       </c>
       <c r="K176" s="5" t="inlineStr">
@@ -9278,17 +9278,17 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Pure red cell aplasia</t>
+          <t>Secondary Raynaud's phenomenon</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>50715003</t>
+          <t>356198000</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Pure red cell aplasia</t>
+          <t>Secondary Raynaud's phenomenon</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9308,13 +9308,13 @@
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>140065</t>
+          <t>4229162</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr"/>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>50715003</t>
+          <t>356198000, 266261006</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
@@ -9331,17 +9331,17 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Pyoderma gangrenosum</t>
+          <t>Reactive arthritis</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>74578003</t>
+          <t>201736002</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Pyoderma gangrenosum</t>
+          <t>Reactive arthritis</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9361,13 +9361,13 @@
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>133283</t>
+          <t>40399768</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>74578003</t>
+          <t>201736002, 67224007</t>
         </is>
       </c>
       <c r="K178" s="5" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Rasmussen syndrome</t>
+          <t>Relapsing polychondritis</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>230191005</t>
+          <t>72275000</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Rasmussen syndrome</t>
+          <t>Relapsing polychondritis</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9414,13 +9414,13 @@
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>4041672</t>
+          <t>4216873</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr"/>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>230191005, 435341000124104</t>
+          <t>72275000</t>
         </is>
       </c>
       <c r="K179" s="5" t="inlineStr">
@@ -9437,17 +9437,17 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Secondary Raynaud's phenomenon</t>
+          <t>Restless legs</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>356198000</t>
+          <t>32914008</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Secondary Raynaud's phenomenon</t>
+          <t>Restless legs</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -9467,13 +9467,13 @@
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>4229162</t>
+          <t>73754</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr"/>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>356198000, 266261006</t>
+          <t>32914008</t>
         </is>
       </c>
       <c r="K180" s="5" t="inlineStr">
@@ -9490,17 +9490,17 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Reactive arthritis</t>
+          <t>Retinocochleocerebral vasculopathy</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>201736002</t>
+          <t>702575003</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>Reactive arthritis</t>
+          <t>Retinocochleocerebral vasculopathy</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -9520,13 +9520,13 @@
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>40399768</t>
+          <t>45765600</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr"/>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>201736002, 67224007</t>
+          <t>702575003</t>
         </is>
       </c>
       <c r="K181" s="5" t="inlineStr">
@@ -9543,22 +9543,22 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Relapsing polychondritis</t>
+          <t>Rheumatic Chorea</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>72275000</t>
+          <t>46826000</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Relapsing polychondritis</t>
+          <t>Rheumatic chorea</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -9573,13 +9573,13 @@
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
-          <t>4216873</t>
+          <t>444120</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr"/>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>72275000</t>
+          <t>46826000</t>
         </is>
       </c>
       <c r="K182" s="5" t="inlineStr">
@@ -9596,17 +9596,17 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Restless legs</t>
+          <t>Rheumatic fever</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>32914008</t>
+          <t>58718002</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Restless legs</t>
+          <t>Rheumatic fever</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9626,13 +9626,13 @@
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>73754</t>
+          <t>442313</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr"/>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>32914008</t>
+          <t>58718002, 194709000</t>
         </is>
       </c>
       <c r="K183" s="5" t="inlineStr">
@@ -9649,17 +9649,17 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Retinocochleocerebral vasculopathy</t>
+          <t>Rheumatoid aortitis</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>702575003</t>
+          <t>38877003</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Retinocochleocerebral vasculopathy</t>
+          <t>Rheumatoid aortitis</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -9679,13 +9679,13 @@
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
-          <t>45765600</t>
+          <t>4306357</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr"/>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>702575003</t>
+          <t>38877003</t>
         </is>
       </c>
       <c r="K184" s="5" t="inlineStr">
@@ -9702,22 +9702,22 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic Chorea</t>
+          <t>Rheumatoid arthritis</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>46826000</t>
+          <t>69896004</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic chorea</t>
+          <t>Rheumatoid arthritis</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
@@ -9732,13 +9732,13 @@
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>444120</t>
+          <t>80809</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr"/>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>46826000</t>
+          <t>69896004</t>
         </is>
       </c>
       <c r="K185" s="5" t="inlineStr">
@@ -9755,17 +9755,17 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic chorea</t>
+          <t>Rheumatoid vasculitis</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>46826000</t>
+          <t>400054000</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic chorea</t>
+          <t>Rheumatoid vasculitis</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -9785,13 +9785,13 @@
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>444120</t>
+          <t>4271003</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr"/>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>46826000</t>
+          <t>400054000</t>
         </is>
       </c>
       <c r="K186" s="5" t="inlineStr">
@@ -9808,17 +9808,17 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic fever</t>
+          <t>Sarcoidosis</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>58718002</t>
+          <t>31541009</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic fever</t>
+          <t>Sarcoidosis</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -9838,13 +9838,13 @@
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t>442313</t>
+          <t>438688</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr"/>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>58718002, 194709000</t>
+          <t>72470008, 238676008, 31541009</t>
         </is>
       </c>
       <c r="K187" s="5" t="inlineStr">
@@ -9861,17 +9861,17 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid aortitis</t>
+          <t>Schnitzler syndrome</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>38877003</t>
+          <t>402415001</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid aortitis</t>
+          <t>Schnitzler syndrome</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -9891,13 +9891,13 @@
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
-          <t>4306357</t>
+          <t>4297647</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr"/>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>38877003</t>
+          <t>402415001</t>
         </is>
       </c>
       <c r="K188" s="5" t="inlineStr">
@@ -9914,17 +9914,17 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid arthritis</t>
+          <t>Scleritis</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>69896004</t>
+          <t>78370002</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid arthritis</t>
+          <t>Scleritis</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -9944,13 +9944,13 @@
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>80809</t>
+          <t>434944</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr"/>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>69896004</t>
+          <t>78370002</t>
         </is>
       </c>
       <c r="K189" s="5" t="inlineStr">
@@ -9967,17 +9967,17 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid vasculitis</t>
+          <t>Sjögren's disease</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>400054000</t>
+          <t>302896008</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid vasculitis</t>
+          <t>Keratoconjunctivitis sicca</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -9992,25 +9992,21 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Keratoconjunctivitis sicca</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
-          <t>4271003</t>
+          <t>4120320</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr"/>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>400054000</t>
-        </is>
-      </c>
-      <c r="K190" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>83901003</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -10020,17 +10016,17 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Sarcoidosis</t>
+          <t>SLE glomerulonephritis syndrome</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>31541009</t>
+          <t>68815009</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Sarcoidosis</t>
+          <t>SLE glomerulonephritis syndrome</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10050,13 +10046,13 @@
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>438688</t>
+          <t>4285717</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr"/>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>72470008, 238676008, 31541009</t>
+          <t>68815009</t>
         </is>
       </c>
       <c r="K191" s="5" t="inlineStr">
@@ -10073,17 +10069,17 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Schnitzler syndrome</t>
+          <t>Small fiber neuropathy</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>402415001</t>
+          <t>709489006</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Schnitzler syndrome</t>
+          <t>Small fiber neuropathy</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10103,13 +10099,13 @@
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
-          <t>4297647</t>
+          <t>46271378</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr"/>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>402415001</t>
+          <t>709489006</t>
         </is>
       </c>
       <c r="K192" s="5" t="inlineStr">
@@ -10126,17 +10122,17 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Scleritis</t>
+          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>78370002</t>
+          <t>771271000</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Scleritis</t>
+          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10156,13 +10152,13 @@
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>434944</t>
+          <t>36674282</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr"/>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>78370002</t>
+          <t>771271000</t>
         </is>
       </c>
       <c r="K193" s="5" t="inlineStr">
@@ -10179,17 +10175,17 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Sjögren's disease</t>
+          <t>Stiff-person syndrome</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>302896008</t>
+          <t>5217008</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Keratoconjunctivitis sicca</t>
+          <t>Stiff-person syndrome</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10204,21 +10200,25 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>Keratoconjunctivitis sicca</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
-          <t>4120320</t>
+          <t>379008</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr"/>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>83901003</t>
-        </is>
-      </c>
-      <c r="K194" s="2" t="inlineStr"/>
+          <t>5217008</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -10228,17 +10228,17 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>SLE glomerulonephritis syndrome</t>
+          <t>Subacute bacterial endocarditis</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>68815009</t>
+          <t>73774007</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>SLE glomerulonephritis syndrome</t>
+          <t>Subacute bacterial endocarditis</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10258,13 +10258,13 @@
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t>4285717</t>
+          <t>4249899</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr"/>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>68815009</t>
+          <t>73774007</t>
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr">
@@ -10281,17 +10281,17 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Small fiber neuropathy</t>
+          <t>Sympathetic uveitis</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>709489006</t>
+          <t>75315001</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Small fiber neuropathy</t>
+          <t>Sympathetic uveitis</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10311,13 +10311,13 @@
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
-          <t>46271378</t>
+          <t>438739</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>709489006</t>
+          <t>75315001</t>
         </is>
       </c>
       <c r="K196" s="5" t="inlineStr">
@@ -10334,17 +10334,17 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
+          <t>Systemic lupus erythematosus</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>771271000</t>
+          <t>55464009</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
+          <t>Systemic lupus erythematosus</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10364,13 +10364,13 @@
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>36674282</t>
+          <t>257628</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr"/>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>771271000</t>
+          <t>55464009</t>
         </is>
       </c>
       <c r="K197" s="5" t="inlineStr">
@@ -10387,17 +10387,17 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Stiff-person syndrome</t>
+          <t>Systemic mast cell disease</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>5217008</t>
+          <t>397016004</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Stiff-person syndrome</t>
+          <t>Systemic mast cell disease</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10417,13 +10417,13 @@
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>379008</t>
+          <t>4246284</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr"/>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>5217008</t>
+          <t>397016004</t>
         </is>
       </c>
       <c r="K198" s="5" t="inlineStr">
@@ -10440,17 +10440,17 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Subacute bacterial endocarditis</t>
+          <t>Systemic sclerosis</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>73774007</t>
+          <t>89155008</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Subacute bacterial endocarditis</t>
+          <t>Systemic sclerosis</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10470,13 +10470,13 @@
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
-          <t>4249899</t>
+          <t>134442</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr"/>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>73774007</t>
+          <t>89155008</t>
         </is>
       </c>
       <c r="K199" s="5" t="inlineStr">
@@ -10493,17 +10493,17 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Sympathetic uveitis</t>
+          <t>Systemic sclerosis with limited cutaneous involvement</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>75315001</t>
+          <t>298285004</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Sympathetic uveitis</t>
+          <t>Systemic sclerosis with limited cutaneous involvement</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10523,13 +10523,13 @@
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t>438739</t>
+          <t>4185187</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr"/>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>75315001</t>
+          <t>298285004, 31848007, 128461001</t>
         </is>
       </c>
       <c r="K200" s="5" t="inlineStr">
@@ -10546,17 +10546,17 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Systemic lupus erythematosus</t>
+          <t>Takayasu's arteritis</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>55464009</t>
+          <t>359789008</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Systemic lupus erythematosus</t>
+          <t>Takayasu's disease</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -10571,18 +10571,18 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Takayasu's disease</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
-          <t>257628</t>
+          <t>440740</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr"/>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>55464009</t>
+          <t>359789008</t>
         </is>
       </c>
       <c r="K201" s="5" t="inlineStr">
@@ -10599,17 +10599,17 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Systemic mast cell disease</t>
+          <t>Temporal arteritis</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>397016004</t>
+          <t>400130008</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Systemic mast cell disease</t>
+          <t>Temporal arteritis</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -10629,13 +10629,13 @@
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
-          <t>4246284</t>
+          <t>4290976</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr"/>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>397016004</t>
+          <t>400130008</t>
         </is>
       </c>
       <c r="K202" s="5" t="inlineStr">
@@ -10652,50 +10652,22 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis</t>
-        </is>
-      </c>
-      <c r="C203" s="4" t="inlineStr">
-        <is>
-          <t>89155008</t>
-        </is>
-      </c>
-      <c r="D203" s="3" t="inlineStr">
-        <is>
-          <t>Systemic sclerosis</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F203" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>TIF1-gamma positive dermatomyositis</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr"/>
+      <c r="D203" s="3" t="inlineStr"/>
+      <c r="E203" s="2" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H203" s="4" t="inlineStr">
-        <is>
-          <t>134442</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr"/>
       <c r="I203" s="2" t="inlineStr"/>
-      <c r="J203" s="3" t="inlineStr">
-        <is>
-          <t>89155008</t>
-        </is>
-      </c>
-      <c r="K203" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J203" s="3" t="inlineStr"/>
+      <c r="K203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -10705,17 +10677,17 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis with limited cutaneous involvement</t>
+          <t>Tolosa-Hunt syndrome</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>298285004</t>
+          <t>95794005</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis with limited cutaneous involvement</t>
+          <t>Tolosa-Hunt syndrome</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -10735,13 +10707,13 @@
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>4185187</t>
+          <t>4317989</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>298285004, 31848007, 128461001</t>
+          <t>95794005</t>
         </is>
       </c>
       <c r="K204" s="5" t="inlineStr">
@@ -10758,43 +10730,43 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Takayasu's arteritis</t>
+          <t>Transverse myelitis</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>359789008</t>
+          <t>16631009</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Takayasu's disease</t>
+          <t>Transverse myelopathy syndrome</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>Takayasu's disease</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t>440740</t>
+          <t>443904</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr"/>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>359789008</t>
+          <t>16631009</t>
         </is>
       </c>
       <c r="K205" s="5" t="inlineStr">
@@ -10811,17 +10783,17 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Temporal arteritis</t>
+          <t>Ulcerative colitis</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>400130008</t>
+          <t>64766004</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Temporal arteritis</t>
+          <t>Ulcerative colitis</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -10841,13 +10813,13 @@
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
-          <t>4290976</t>
+          <t>81893</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr"/>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>400130008</t>
+          <t>64766004</t>
         </is>
       </c>
       <c r="K206" s="5" t="inlineStr">
@@ -10864,22 +10836,50 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>TIF1-gamma positive dermatomyositis</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr"/>
-      <c r="D207" s="3" t="inlineStr"/>
-      <c r="E207" s="2" t="inlineStr"/>
-      <c r="F207" s="2" t="inlineStr"/>
+          <t>Undifferentiated connective tissue disease</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>239918008</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Undifferentiated connective tissue disease</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H207" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H207" s="4" t="inlineStr">
+        <is>
+          <t>4344165</t>
+        </is>
+      </c>
       <c r="I207" s="2" t="inlineStr"/>
-      <c r="J207" s="3" t="inlineStr"/>
-      <c r="K207" s="2" t="inlineStr"/>
+      <c r="J207" s="3" t="inlineStr">
+        <is>
+          <t>239918008</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -10889,50 +10889,26 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Tolosa-Hunt syndrome</t>
-        </is>
-      </c>
-      <c r="C208" s="4" t="inlineStr">
-        <is>
-          <t>95794005</t>
-        </is>
-      </c>
-      <c r="D208" s="3" t="inlineStr">
-        <is>
-          <t>Tolosa-Hunt syndrome</t>
-        </is>
-      </c>
-      <c r="E208" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F208" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Urticarial vasculitis</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr"/>
+      <c r="D208" s="3" t="inlineStr"/>
+      <c r="E208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H208" s="4" t="inlineStr">
-        <is>
-          <t>4317989</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr"/>
       <c r="I208" s="2" t="inlineStr"/>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>95794005</t>
-        </is>
-      </c>
-      <c r="K208" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>402656007</t>
+        </is>
+      </c>
+      <c r="K208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -10942,27 +10918,27 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Transverse myelitis</t>
+          <t>Uveitis</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>16631009</t>
+          <t>128473001</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Transverse myelopathy syndrome</t>
+          <t>Uveitis</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>name</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -10972,13 +10948,13 @@
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>443904</t>
+          <t>4028363</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr"/>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>16631009</t>
+          <t>128473001, 231947004</t>
         </is>
       </c>
       <c r="K209" s="5" t="inlineStr">
@@ -10995,17 +10971,17 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Ulcerative colitis</t>
+          <t>Vitiligo</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>64766004</t>
+          <t>56727007</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Ulcerative colitis</t>
+          <t>Vitiligo</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11025,13 +11001,13 @@
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
-          <t>81893</t>
+          <t>138502</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr"/>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>64766004</t>
+          <t>56727007</t>
         </is>
       </c>
       <c r="K210" s="5" t="inlineStr">
@@ -11048,17 +11024,17 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Undifferentiated connective tissue disease</t>
+          <t>Vogt-Koyanagi-Harada disease</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>239918008</t>
+          <t>193497004</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Undifferentiated connective tissue disease</t>
+          <t>Vogt-Koyanagi-Harada disease</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -11078,13 +11054,13 @@
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
-          <t>4344165</t>
+          <t>4108968</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr"/>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>239918008</t>
+          <t>193497004</t>
         </is>
       </c>
       <c r="K211" s="5" t="inlineStr">
@@ -11101,234 +11077,46 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Urticarial vasculitis</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr"/>
-      <c r="D212" s="3" t="inlineStr"/>
-      <c r="E212" s="2" t="inlineStr"/>
-      <c r="F212" s="2" t="inlineStr"/>
+          <t>Warm autoimmune hemolytic anemia</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>3978000</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Warm autoimmune hemolytic anemia</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H212" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H212" s="4" t="inlineStr">
+        <is>
+          <t>4219853</t>
+        </is>
+      </c>
       <c r="I212" s="2" t="inlineStr"/>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>402656007</t>
-        </is>
-      </c>
-      <c r="K212" s="2" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>ARI:0001212</t>
-        </is>
-      </c>
-      <c r="B213" s="3" t="inlineStr">
-        <is>
-          <t>Uveitis</t>
-        </is>
-      </c>
-      <c r="C213" s="4" t="inlineStr">
-        <is>
-          <t>128473001</t>
-        </is>
-      </c>
-      <c r="D213" s="3" t="inlineStr">
-        <is>
-          <t>Uveitis</t>
-        </is>
-      </c>
-      <c r="E213" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F213" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G213" s="3" t="inlineStr">
-        <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H213" s="4" t="inlineStr">
-        <is>
-          <t>4028363</t>
-        </is>
-      </c>
-      <c r="I213" s="2" t="inlineStr"/>
-      <c r="J213" s="3" t="inlineStr">
-        <is>
-          <t>128473001, 231947004</t>
-        </is>
-      </c>
-      <c r="K213" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>ARI:0001213</t>
-        </is>
-      </c>
-      <c r="B214" s="3" t="inlineStr">
-        <is>
-          <t>Vitiligo</t>
-        </is>
-      </c>
-      <c r="C214" s="4" t="inlineStr">
-        <is>
-          <t>56727007</t>
-        </is>
-      </c>
-      <c r="D214" s="3" t="inlineStr">
-        <is>
-          <t>Vitiligo</t>
-        </is>
-      </c>
-      <c r="E214" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F214" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G214" s="3" t="inlineStr">
-        <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H214" s="4" t="inlineStr">
-        <is>
-          <t>138502</t>
-        </is>
-      </c>
-      <c r="I214" s="2" t="inlineStr"/>
-      <c r="J214" s="3" t="inlineStr">
-        <is>
-          <t>56727007</t>
-        </is>
-      </c>
-      <c r="K214" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>ARI:0001214</t>
-        </is>
-      </c>
-      <c r="B215" s="3" t="inlineStr">
-        <is>
-          <t>Vogt-Koyanagi-Harada disease</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr">
-        <is>
-          <t>193497004</t>
-        </is>
-      </c>
-      <c r="D215" s="3" t="inlineStr">
-        <is>
-          <t>Vogt-Koyanagi-Harada disease</t>
-        </is>
-      </c>
-      <c r="E215" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F215" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G215" s="3" t="inlineStr">
-        <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H215" s="4" t="inlineStr">
-        <is>
-          <t>4108968</t>
-        </is>
-      </c>
-      <c r="I215" s="2" t="inlineStr"/>
-      <c r="J215" s="3" t="inlineStr">
-        <is>
-          <t>193497004</t>
-        </is>
-      </c>
-      <c r="K215" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>ARI:0001215</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="inlineStr">
-        <is>
-          <t>Warm autoimmune hemolytic anemia</t>
-        </is>
-      </c>
-      <c r="C216" s="4" t="inlineStr">
-        <is>
           <t>3978000</t>
         </is>
       </c>
-      <c r="D216" s="3" t="inlineStr">
-        <is>
-          <t>Warm autoimmune hemolytic anemia</t>
-        </is>
-      </c>
-      <c r="E216" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F216" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G216" s="3" t="inlineStr">
-        <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H216" s="4" t="inlineStr">
-        <is>
-          <t>4219853</t>
-        </is>
-      </c>
-      <c r="I216" s="2" t="inlineStr"/>
-      <c r="J216" s="3" t="inlineStr">
-        <is>
-          <t>3978000</t>
-        </is>
-      </c>
-      <c r="K216" s="5" t="inlineStr">
+      <c r="K212" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -11517,8 +11305,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId185"/>
@@ -11557,10 +11345,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId219"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId225"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId227"/>
@@ -11591,20 +11379,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId253"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId261"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId268"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId269"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId270"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId271"/>
@@ -11633,12 +11421,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId295"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId302"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId303"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId304"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId305"/>
@@ -11699,30 +11487,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId360"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId361"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId378"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/4-reports/7_SNOMED_Matches_All.xlsx
+++ b/data/4-reports/7_SNOMED_Matches_All.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K212"/>
+  <dimension ref="A1:K211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1716,17 +1716,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune disease</t>
+          <t>Autoimmune disorder of inner ear</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>85828009</t>
+          <t>232308006</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune disease</t>
+          <t>Autoimmune disorder of inner ear</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1746,13 +1746,13 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>434621</t>
+          <t>4337463</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>85828009</t>
+          <t>232308006, 13445001</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -1769,17 +1769,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune disorder of inner ear</t>
+          <t>Autoimmune encephalitis</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>232308006</t>
+          <t>95643007</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune disorder of inner ear</t>
+          <t>Autoimmune encephalitis</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1799,13 +1799,13 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>4337463</t>
+          <t>4318558</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>232308006, 13445001</t>
+          <t>95643007</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -1822,17 +1822,17 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune encephalitis</t>
+          <t>Autoimmune encephalitis caused by N-methyl D-aspartate receptor antibody</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>95643007</t>
+          <t>452281000124106</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune encephalitis</t>
+          <t>Autoimmune encephalitis caused by N-methyl D-aspartate receptor antibody</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1852,13 +1852,13 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>4318558</t>
+          <t>764228</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>95643007</t>
+          <t>452281000124106, 716684004</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune encephalitis caused by N-methyl D-aspartate receptor antibody</t>
+          <t>Autoimmune ganglionopathy</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>452281000124106</t>
+          <t>838330008</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune encephalitis caused by N-methyl D-aspartate receptor antibody</t>
+          <t>Autoimmune ganglionopathy</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1905,13 +1905,13 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>764228</t>
+          <t>3654638</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>452281000124106, 716684004</t>
+          <t>838330008, 838321000</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -1928,17 +1928,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune ganglionopathy</t>
+          <t>Autoimmune gastritis</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>838330008</t>
+          <t>84568007</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune ganglionopathy</t>
+          <t>Atrophic gastritis</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1953,18 +1953,18 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Atrophic gastritis</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>3654638</t>
+          <t>192667</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>838330008, 838321000</t>
+          <t>84568007, 235728001, 84027009</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -1981,17 +1981,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune gastritis</t>
+          <t>Autoimmune hemolytic anemia</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>84568007</t>
+          <t>413603009</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Atrophic gastritis</t>
+          <t>Autoimmune hemolytic anemia</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2006,18 +2006,18 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Atrophic gastritis</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>192667</t>
+          <t>441269</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>84568007, 235728001, 84027009</t>
+          <t>413603009, 718716008</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -2034,17 +2034,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune hemolytic anemia</t>
+          <t>Autoimmune hepatitis</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>413603009</t>
+          <t>408335007</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune hemolytic anemia</t>
+          <t>Autoimmune hepatitis</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2064,13 +2064,13 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>441269</t>
+          <t>200762</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>413603009, 718716008</t>
+          <t>408335007, 721711009, 721712002, 721713007, 16098491000119109</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -2087,17 +2087,17 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune hepatitis</t>
+          <t>Autoimmune hypoparathyroidism</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>408335007</t>
+          <t>75316000</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune hepatitis</t>
+          <t>Autoimmune hypoparathyroidism</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2117,13 +2117,13 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>200762</t>
+          <t>4326738</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>408335007, 721711009, 721712002, 721713007, 16098491000119109</t>
+          <t>75316000</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -2140,17 +2140,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune hypoparathyroidism</t>
+          <t>Autoimmune hypophysitis</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>75316000</t>
+          <t>237706000</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune hypoparathyroidism</t>
+          <t>Autoimmune hypophysitis</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2170,13 +2170,13 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>4326738</t>
+          <t>4030201</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>75316000</t>
+          <t>237706000</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2193,50 +2193,22 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune hypophysitis</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>237706000</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Autoimmune hypophysitis</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Autoimmune-Inflammatory Syndrome Induced by Adjuvants</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>4030201</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>237706000</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2246,22 +2218,50 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune-Inflammatory Syndrome Induced by Adjuvants</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
+          <t>Autoimmune limbic encephalitis</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>1300193002</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Autoimmune limbic encephalitis</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>1245375</t>
+        </is>
+      </c>
       <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>1300193002</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune limbic encephalitis</t>
+          <t>Autoimmune lymphoproliferative syndrome</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1300193002</t>
+          <t>702444009</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune limbic encephalitis</t>
+          <t>Autoimmune lymphoproliferative syndrome</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2301,13 +2301,13 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>1245375</t>
+          <t>45765493</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1300193002</t>
+          <t>702444009</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -2324,17 +2324,17 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune lymphoproliferative syndrome</t>
+          <t>Autoimmune necrotizing myopathy</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>702444009</t>
+          <t>715863001</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune lymphoproliferative syndrome</t>
+          <t>Autoimmune necrotizing myopathy</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2354,13 +2354,13 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>45765493</t>
+          <t>37396156</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>702444009</t>
+          <t>715863001</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -2377,17 +2377,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune necrotizing myopathy</t>
+          <t>Autoimmune neutropenia</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>715863001</t>
+          <t>234425008</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune necrotizing myopathy</t>
+          <t>Autoimmune neutropenia</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2407,13 +2407,13 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>37396156</t>
+          <t>4125635</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>715863001</t>
+          <t>234425008</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune neutropenia</t>
+          <t>Autoimmune oophoritis</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>234425008</t>
+          <t>721198006</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune neutropenia</t>
+          <t>Premature ovarian failure due to autoimmune oophoritis</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2455,18 +2455,18 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Premature ovarian failure due to autoimmune oophoritis</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>4125635</t>
+          <t>36717453</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>234425008</t>
+          <t>721198006</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -2483,17 +2483,17 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune oophoritis</t>
+          <t>Autoimmune optic neuropathy</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>721198006</t>
+          <t>838324008</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Premature ovarian failure due to autoimmune oophoritis</t>
+          <t>Autoimmune optic neuropathy</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2508,18 +2508,18 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Premature ovarian failure due to autoimmune oophoritis</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>36717453</t>
+          <t>3654632</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>721198006</t>
+          <t>838324008</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -2536,17 +2536,17 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune optic neuropathy</t>
+          <t>Autoimmune pancreatitis</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>838324008</t>
+          <t>448542008</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune optic neuropathy</t>
+          <t>Autoimmune pancreatitis</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2566,13 +2566,13 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>3654632</t>
+          <t>40490446</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>838324008</t>
+          <t>448542008, 722872000, 1197740007</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -2589,17 +2589,17 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune pancreatitis</t>
+          <t>Autoimmune progesterone dermatitis</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>448542008</t>
+          <t>838551007</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune pancreatitis</t>
+          <t>Autoimmune progesterone dermatitis</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2619,13 +2619,13 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>40490446</t>
+          <t>3661498</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>448542008, 722872000, 1197740007</t>
+          <t>838551007</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -2642,17 +2642,17 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune progesterone dermatitis</t>
+          <t>Autoimmune pulmonary alveolar proteinosis</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>838551007</t>
+          <t>707443007</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune progesterone dermatitis</t>
+          <t>Autoimmune pulmonary alveolar proteinosis</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2672,13 +2672,13 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>3661498</t>
+          <t>45768909</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>838551007</t>
+          <t>707443007</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
@@ -2695,50 +2695,22 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune pulmonary alveolar proteinosis</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>707443007</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Autoimmune pulmonary alveolar proteinosis</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Autoimmune retinal vasculitis</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>45768909</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>707443007</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2748,22 +2720,50 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune retinal vasculitis</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
+          <t>Autoimmune retinopathy</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>724809006</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Autoimmune retinopathy</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>37110540</t>
+        </is>
+      </c>
       <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="3" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>724809006</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2773,17 +2773,17 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune retinopathy</t>
+          <t>Autoimmune thyroiditis</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>724809006</t>
+          <t>66944004</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune retinopathy</t>
+          <t>Autoimmune thyroiditis</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2803,13 +2803,13 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>37110540</t>
+          <t>4281109</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>724809006</t>
+          <t>66944004, 21983002</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -2826,17 +2826,17 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune thyroiditis</t>
+          <t>Autoimmune urticaria</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>66944004</t>
+          <t>402397006</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune thyroiditis</t>
+          <t>Autoimmune urticaria</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2856,13 +2856,13 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>4281109</t>
+          <t>4224623</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>66944004, 21983002</t>
+          <t>402397006</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -2879,17 +2879,17 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune urticaria</t>
+          <t>Autoimmune urticaria and/or angioedema</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>402397006</t>
+          <t>402402005</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune urticaria</t>
+          <t>Autoimmune urticaria and/or angioedema</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2909,13 +2909,13 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>4224623</t>
+          <t>4221673</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>402397006</t>
+          <t>402402005</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -2932,17 +2932,17 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune urticaria and/or angioedema</t>
+          <t>Autoimmune vasculitis</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>402402005</t>
+          <t>427213005</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune urticaria and/or angioedema</t>
+          <t>Autoimmune vasculitis</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2962,13 +2962,13 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>4221673</t>
+          <t>4146124</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>402402005</t>
+          <t>427213005</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -2985,17 +2985,17 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune vasculitis</t>
+          <t>Balo concentric sclerosis</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>427213005</t>
+          <t>230380005</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune vasculitis</t>
+          <t>Balo concentric sclerosis</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3015,13 +3015,13 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>4146124</t>
+          <t>4046110</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>427213005</t>
+          <t>230380005</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -3038,17 +3038,17 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Balo concentric sclerosis</t>
+          <t>Behçet's syndrome</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>230380005</t>
+          <t>310701003</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Balo concentric sclerosis</t>
+          <t>Behcet's syndrome</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3063,18 +3063,18 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Behcet's syndrome</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>4046110</t>
+          <t>436642</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>230380005</t>
+          <t>310701003, 721226005</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -3091,17 +3091,17 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Behçet's syndrome</t>
+          <t>Benign mucous membrane pemphigoid</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>310701003</t>
+          <t>34250006</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Behcet's syndrome</t>
+          <t>Benign mucous membrane pemphigoid</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3116,18 +3116,18 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Behcet's syndrome</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>436642</t>
+          <t>4142060</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>310701003, 721226005</t>
+          <t>34250006, 314757003</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
@@ -3144,17 +3144,17 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Benign mucous membrane pemphigoid</t>
+          <t>Bickerstaff's brainstem encephalitis</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>34250006</t>
+          <t>427086003</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Benign mucous membrane pemphigoid</t>
+          <t>Bickerstaff's brainstem encephalitis</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3174,13 +3174,13 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>4142060</t>
+          <t>4141686</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>34250006, 314757003</t>
+          <t>427086003</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -3197,17 +3197,17 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Bickerstaff's brainstem encephalitis</t>
+          <t>Birdshot chorioretinopathy</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>427086003</t>
+          <t>231981005</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Bickerstaff's brainstem encephalitis</t>
+          <t>Birdshot chorioretinitis</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3222,18 +3222,18 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Birdshot chorioretinitis</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>4141686</t>
+          <t>4334133</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>427086003</t>
+          <t>231981005</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -3250,17 +3250,17 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Birdshot chorioretinopathy</t>
+          <t>Bullous pemphigoid</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>231981005</t>
+          <t>77090002</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Birdshot chorioretinitis</t>
+          <t>Bullous pemphigoid</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3275,18 +3275,18 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Birdshot chorioretinitis</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>4334133</t>
+          <t>4298692</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>231981005</t>
+          <t>77090002</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Bullous pemphigoid</t>
+          <t>Bullous systemic lupus erythematosus</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>77090002</t>
+          <t>239889005</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Bullous pemphigoid</t>
+          <t>Bullous systemic lupus erythematosus</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3333,13 +3333,13 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>4298692</t>
+          <t>4346976</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>77090002</t>
+          <t>239889005</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Bullous systemic lupus erythematosus</t>
+          <t>Calcinosis due to childhood type dermatomyositis</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>239889005</t>
+          <t>838312001</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Bullous systemic lupus erythematosus</t>
+          <t>Calcinosis due to childhood type dermatomyositis</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3386,13 +3386,13 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>4346976</t>
+          <t>3654620</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>239889005</t>
+          <t>838312001</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
@@ -3409,17 +3409,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Calcinosis due to childhood type dermatomyositis</t>
+          <t>Cataplexy and narcolepsy</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>838312001</t>
+          <t>193042000</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Calcinosis due to childhood type dermatomyositis</t>
+          <t>Cataplexy and narcolepsy</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3439,13 +3439,13 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>3654620</t>
+          <t>437854</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>838312001</t>
+          <t>193042000, 735676003</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Cataplexy and narcolepsy</t>
+          <t>Celiac disease</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>193042000</t>
+          <t>396331005</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Cataplexy and narcolepsy</t>
+          <t>Celiac disease</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3492,13 +3492,13 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>437854</t>
+          <t>194992</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>193042000, 735676003</t>
+          <t>91867008, 396331005</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
@@ -3515,22 +3515,22 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Celiac disease</t>
+          <t>Chronic Fatigue Syndrome</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>396331005</t>
+          <t>52702003</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Celiac disease</t>
+          <t>Chronic fatigue syndrome</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3545,13 +3545,13 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>194992</t>
+          <t>432738</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>91867008, 396331005</t>
+          <t>52702003</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
@@ -3568,22 +3568,22 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Chronic Fatigue Syndrome</t>
+          <t>Chronic inflammatory demyelinating polyradiculoneuropathy</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>52702003</t>
+          <t>128209004</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Chronic fatigue syndrome</t>
+          <t>Chronic inflammatory demyelinating polyradiculoneuropathy</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3598,13 +3598,13 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>432738</t>
+          <t>381009</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>52702003</t>
+          <t>128209004, 230564004</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
@@ -3621,27 +3621,27 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Chronic inflammatory demyelinating polyradiculoneuropathy</t>
+          <t>Chronic interstitial cystitis</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>128209004</t>
+          <t>38731000087104</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Chronic inflammatory demyelinating polyradiculoneuropathy</t>
+          <t>Chronic primary bladder pain syndrome</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -3651,20 +3651,16 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>381009</t>
+          <t>1450471</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>128209004, 230564004</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>197834003</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3674,46 +3670,50 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Chronic interstitial cystitis</t>
+          <t>Chronic Lyme disease</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>38731000087104</t>
+          <t>23502006</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Chronic primary bladder pain syndrome</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>name</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>1450471</t>
+          <t>440638</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>197834003</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr"/>
+          <t>33937009, 23502006</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3723,50 +3723,26 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Chronic Lyme disease</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>23502006</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Lyme disease</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Chronic multifocal osteomyelitis</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>440638</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>33937009, 23502006</t>
-        </is>
-      </c>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>240151005</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3776,7 +3752,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Chronic multifocal osteomyelitis</t>
+          <t>Chronic post-COVID-19 syndrome</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr"/>
@@ -3792,7 +3768,7 @@
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>240151005</t>
+          <t>1119304009</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
@@ -3805,26 +3781,50 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Chronic post-COVID-19 syndrome</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr"/>
+          <t>Cogan's syndrome</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>405810005</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Cogan's syndrome</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>4233620</t>
+        </is>
+      </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>1119304009</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr"/>
+          <t>405810005</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3834,17 +3834,17 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Cogan's syndrome</t>
+          <t>Cold agglutinin disease</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>405810005</t>
+          <t>398937006</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Cogan's syndrome</t>
+          <t>Cold autoimmune hemolytic anemia</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3859,18 +3859,18 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Cold autoimmune hemolytic anemia</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>4233620</t>
+          <t>4160887</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>405810005</t>
+          <t>398937006, 127055007</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
@@ -3887,17 +3887,17 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Cold agglutinin disease</t>
+          <t>Combined immunodeficiency due to LRBA deficiency</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>398937006</t>
+          <t>1197477000</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Cold autoimmune hemolytic anemia</t>
+          <t>Combined immunodeficiency due to LRBA deficiency</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3912,18 +3912,18 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Cold autoimmune hemolytic anemia</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>4160887</t>
+          <t>37162777</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>398937006, 127055007</t>
+          <t>1197477000</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
@@ -3940,17 +3940,17 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Combined immunodeficiency due to LRBA deficiency</t>
+          <t>Complex regional pain syndrome</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1197477000</t>
+          <t>128200000</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Combined immunodeficiency due to LRBA deficiency</t>
+          <t>Complex regional pain syndrome</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3970,13 +3970,13 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>37162777</t>
+          <t>4134577</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>1197477000</t>
+          <t>128200000, 408751001, 734947007</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
@@ -3993,50 +3993,22 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Complex regional pain syndrome</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>128200000</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Complex regional pain syndrome</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>COPA syndrome</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>4134577</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>128200000, 408751001, 734947007</t>
-        </is>
-      </c>
-      <c r="K72" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J72" s="3" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4046,22 +4018,50 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>COPA syndrome</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr"/>
-      <c r="D73" s="3" t="inlineStr"/>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
+          <t>Crohn's disease</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>34000006</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Crohn's disease</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>201606</t>
+        </is>
+      </c>
       <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="3" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>34000006</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4071,17 +4071,17 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Crohn's disease</t>
+          <t>Cryptogenic organizing pneumonia</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>34000006</t>
+          <t>719218000</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Crohn's disease</t>
+          <t>Cryptogenic organizing pneumonia</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4101,13 +4101,13 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>201606</t>
+          <t>36714118</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>34000006</t>
+          <t>719218000</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
@@ -4124,50 +4124,22 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Cryptogenic organizing pneumonia</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>719218000</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Cryptogenic organizing pneumonia</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>CTLA4 haploinsufficiency</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>36714118</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>719218000</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4177,22 +4149,50 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>CTLA4 haploinsufficiency</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr"/>
-      <c r="D76" s="3" t="inlineStr"/>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
+          <t>Cutaneous lupus erythematosus</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>7119001</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Cutaneous lupus erythematosus</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>4324123</t>
+        </is>
+      </c>
       <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="3" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>238927000, 7119001, 200938002, 403495008, 200941006, 239891002</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4202,17 +4202,17 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Cutaneous lupus erythematosus</t>
+          <t>Cutaneous mastocytosis</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>7119001</t>
+          <t>397012002</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Cutaneous lupus erythematosus</t>
+          <t>Cutaneous mastocytosis</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4232,13 +4232,13 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>4324123</t>
+          <t>4246283</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>238927000, 7119001, 200938002, 403495008, 200941006, 239891002</t>
+          <t>397012002</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Cutaneous mastocytosis</t>
+          <t>Dermatitis herpetiformis</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>397012002</t>
+          <t>111196000</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Cutaneous mastocytosis</t>
+          <t>Dermatitis herpetiformis</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4285,13 +4285,13 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>4246283</t>
+          <t>140487</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>397012002</t>
+          <t>111196000</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
@@ -4308,17 +4308,17 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Dermatitis herpetiformis</t>
+          <t>Dermatomyositis</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>111196000</t>
+          <t>396230008</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Dermatitis herpetiformis</t>
+          <t>Dermatomyositis</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4338,13 +4338,13 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>140487</t>
+          <t>80182</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>111196000</t>
+          <t>396230008, 1212005</t>
         </is>
       </c>
       <c r="K79" s="5" t="inlineStr">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Dermatomyositis</t>
+          <t>Diabetes mellitus type 1</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>396230008</t>
+          <t>46635009</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Dermatomyositis</t>
+          <t>Type 1 diabetes mellitus</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4386,18 +4386,18 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Type 1 diabetes mellitus</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>80182</t>
+          <t>201254</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>396230008, 1212005</t>
+          <t>46635009</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
@@ -4414,17 +4414,17 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Diabetes mellitus type 1</t>
+          <t>Eaton-Lambert syndrome</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>46635009</t>
+          <t>56989000</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Type 1 diabetes mellitus</t>
+          <t>Eaton-Lambert syndrome</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4439,18 +4439,18 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>Type 1 diabetes mellitus</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>201254</t>
+          <t>4237155</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>46635009</t>
+          <t>56989000</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr">
@@ -4467,50 +4467,22 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Eaton-Lambert syndrome</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>56989000</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>Eaton-Lambert syndrome</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Encephalitis caused by anti-gamma-aminobutyric acid-A receptor antibody</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="3" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>4237155</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>56989000</t>
-        </is>
-      </c>
-      <c r="K82" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J82" s="3" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4520,7 +4492,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Encephalitis caused by anti-gamma-aminobutyric acid-A receptor antibody</t>
+          <t>Encephalopathy caused by anti-IgLON5 antibody</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr"/>
@@ -4545,22 +4517,50 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Encephalopathy caused by anti-IgLON5 antibody</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr"/>
-      <c r="D84" s="3" t="inlineStr"/>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>129103003</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Endometriosis (clinical)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>0.556</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>synonym</t>
+        </is>
+      </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>433527</t>
+        </is>
+      </c>
       <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="3" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>129103003</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4570,27 +4570,27 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Endometriosis</t>
+          <t>Enthesitis</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>129103003</t>
+          <t>359643005</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Endometriosis (clinical)</t>
+          <t>Enthesitis</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>name</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -4600,13 +4600,13 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>433527</t>
+          <t>4231746</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>129103003</t>
+          <t>359643005</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr">
@@ -4623,17 +4623,17 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Enthesitis</t>
+          <t>Eosinophilic esophagitis</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>359643005</t>
+          <t>235599003</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Enthesitis</t>
+          <t>Eosinophilic esophagitis</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4653,13 +4653,13 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>4231746</t>
+          <t>27918</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>359643005</t>
+          <t>235599003</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
@@ -4676,17 +4676,17 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Eosinophilic esophagitis</t>
+          <t>Epilepsy</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>235599003</t>
+          <t>84757009</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Eosinophilic esophagitis</t>
+          <t>Epilepsy</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4706,13 +4706,13 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>27918</t>
+          <t>380378</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>235599003</t>
+          <t>84757009</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr">
@@ -4729,17 +4729,17 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Epilepsy</t>
+          <t>Episcleritis</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>84757009</t>
+          <t>815008</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Epilepsy</t>
+          <t>Episcleritis</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4759,13 +4759,13 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>380378</t>
+          <t>4218083</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>84757009</t>
+          <t>815008</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Episcleritis</t>
+          <t>Erythema nodosum</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>815008</t>
+          <t>32861005</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Episcleritis</t>
+          <t>Erythema nodosum</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4812,13 +4812,13 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>4218083</t>
+          <t>140176</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>815008</t>
+          <t>32861005</t>
         </is>
       </c>
       <c r="K89" s="5" t="inlineStr">
@@ -4835,17 +4835,17 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Erythema nodosum</t>
+          <t>Essential mixed cryoglobulinemia</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>32861005</t>
+          <t>239947001</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Erythema nodosum</t>
+          <t>Essential mixed cryoglobulinemia</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4865,13 +4865,13 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>140176</t>
+          <t>4347067</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>32861005</t>
+          <t>239947001</t>
         </is>
       </c>
       <c r="K90" s="5" t="inlineStr">
@@ -4888,17 +4888,17 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Essential mixed cryoglobulinemia</t>
+          <t>Evans syndrome</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>239947001</t>
+          <t>75331009</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Essential mixed cryoglobulinemia</t>
+          <t>Evans syndrome</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4918,13 +4918,13 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>4347067</t>
+          <t>436956</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>239947001</t>
+          <t>75331009</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
@@ -4941,17 +4941,17 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Evans syndrome</t>
+          <t>Fasciitis with eosinophilia syndrome</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>75331009</t>
+          <t>24129002</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Evans syndrome</t>
+          <t>Fasciitis with eosinophilia syndrome</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4971,13 +4971,13 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>436956</t>
+          <t>4083100</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>75331009</t>
+          <t>24129002</t>
         </is>
       </c>
       <c r="K92" s="5" t="inlineStr">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Fasciitis with eosinophilia syndrome</t>
+          <t>Felty syndrome</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>24129002</t>
+          <t>57160007</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Fasciitis with eosinophilia syndrome</t>
+          <t>Felty's syndrome</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5019,18 +5019,18 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Felty's syndrome</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>4083100</t>
+          <t>81097</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>24129002</t>
+          <t>57160007</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
@@ -5047,22 +5047,22 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Felty syndrome</t>
+          <t>Female infertility due to antisperm antibodies</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>57160007</t>
+          <t>414238007</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Felty's syndrome</t>
+          <t>Female infertility due to antisperm antibody</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -5072,18 +5072,18 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>Felty's syndrome</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>81097</t>
+          <t>4188008</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>57160007</t>
+          <t>414238007, 236816007</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Female infertility due to antisperm antibodies</t>
+          <t>Fibromyalgia</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>414238007</t>
+          <t>203082005</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Female infertility due to antisperm antibody</t>
+          <t>Fibromyalgia</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -5130,13 +5130,13 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>4188008</t>
+          <t>40405599</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>414238007, 236816007</t>
+          <t>203082005</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
@@ -5153,17 +5153,17 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Fibromyalgia</t>
+          <t>Graves' disease</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>203082005</t>
+          <t>353295004</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Fibromyalgia</t>
+          <t>Graves' disease</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5183,13 +5183,13 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>40405599</t>
+          <t>4232076</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>203082005</t>
+          <t>353295004, 90739004, 237499004</t>
         </is>
       </c>
       <c r="K96" s="5" t="inlineStr">
@@ -5206,17 +5206,17 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Graves' disease</t>
+          <t>Guillain-Barré syndrome</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>353295004</t>
+          <t>40956001</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Graves' disease</t>
+          <t>Guillain-Barré syndrome</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5236,13 +5236,13 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>4232076</t>
+          <t>4164770</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>353295004, 90739004, 237499004</t>
+          <t>715770009, 1767005, 40956001, 716723000</t>
         </is>
       </c>
       <c r="K97" s="5" t="inlineStr">
@@ -5259,17 +5259,17 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Guillain-Barré syndrome</t>
+          <t>Hemophilia B Leyden</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>40956001</t>
+          <t>1336117005</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Guillain-Barré syndrome</t>
+          <t>Hemophilia B Leyden</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5289,13 +5289,13 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>4164770</t>
+          <t>1076202</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>715770009, 1767005, 40956001, 716723000</t>
+          <t>1336117005</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Hemophilia B Leyden</t>
+          <t>Herpes gestationis</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>1336117005</t>
+          <t>86081009</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Hemophilia B Leyden</t>
+          <t>Herpes gestationis</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5342,13 +5342,13 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>1076202</t>
+          <t>4311256</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>1336117005</t>
+          <t>86081009</t>
         </is>
       </c>
       <c r="K99" s="5" t="inlineStr">
@@ -5365,17 +5365,17 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Herpes gestationis</t>
+          <t>Hidradenitis suppurativa</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>86081009</t>
+          <t>59393003</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Herpes gestationis</t>
+          <t>Hidradenitis suppurativa</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5395,13 +5395,13 @@
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>4311256</t>
+          <t>4241223</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>86081009</t>
+          <t>59393003</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
@@ -5418,17 +5418,17 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Hidradenitis suppurativa</t>
+          <t>Hypersensitivity angiitis</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>59393003</t>
+          <t>60555002</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Hidradenitis suppurativa</t>
+          <t>Hypersensitivity angiitis</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5448,13 +5448,13 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>4241223</t>
+          <t>196431</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>59393003</t>
+          <t>60555002</t>
         </is>
       </c>
       <c r="K101" s="5" t="inlineStr">
@@ -5471,17 +5471,17 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Hypersensitivity angiitis</t>
+          <t>Idiopathic membranous glomerulonephritis</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>60555002</t>
+          <t>722119002</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Hypersensitivity angiitis</t>
+          <t>Idiopathic membranous glomerulonephritis</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5501,13 +5501,13 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>196431</t>
+          <t>36716199</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>60555002</t>
+          <t>722119002</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
@@ -5524,17 +5524,17 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Idiopathic membranous glomerulonephritis</t>
+          <t>Idiopathic pulmonary fibrosis</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>722119002</t>
+          <t>700250006</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Idiopathic membranous glomerulonephritis</t>
+          <t>Idiopathic pulmonary fibrosis</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5554,13 +5554,13 @@
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>36716199</t>
+          <t>45763750</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>722119002</t>
+          <t>700250006</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr">
@@ -5577,17 +5577,17 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Idiopathic pulmonary fibrosis</t>
+          <t>IgA nephropathy</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>700250006</t>
+          <t>236407003</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Idiopathic pulmonary fibrosis</t>
+          <t>IgA nephropathy</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5607,13 +5607,13 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>45763750</t>
+          <t>4128061</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>700250006</t>
+          <t>236407003</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr">
@@ -5630,50 +5630,22 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>IgA nephropathy</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>236407003</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>IgA nephropathy</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Immune checkpoint inhibitor-induced autoimmunity</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr"/>
+      <c r="D105" s="3" t="inlineStr"/>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t>4128061</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>236407003</t>
-        </is>
-      </c>
-      <c r="K105" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J105" s="3" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -5683,7 +5655,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Immune checkpoint inhibitor-induced autoimmunity</t>
+          <t>Immune Dysregulation, Polyendocrinopathy, Enteropathy, X-Linked Syndrome</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr"/>
@@ -5708,22 +5680,50 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Immune Dysregulation, Polyendocrinopathy, Enteropathy, X-Linked Syndrome</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr"/>
-      <c r="D107" s="3" t="inlineStr"/>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr"/>
+          <t>Immune thrombocytopenia</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>2897005</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Immune thrombocytopenia</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>4103532</t>
+        </is>
+      </c>
       <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="3" t="inlineStr"/>
-      <c r="K107" s="2" t="inlineStr"/>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>13172003, 128092005, 2897005, 438476003, 32273002, 128091003</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -5733,17 +5733,17 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Immune thrombocytopenia</t>
+          <t>Immunoglobulin A vasculitis</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>2897005</t>
+          <t>191306005</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Immune thrombocytopenia</t>
+          <t>Immunoglobulin A vasculitis</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5763,13 +5763,13 @@
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>4103532</t>
+          <t>4101602</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>13172003, 128092005, 2897005, 438476003, 32273002, 128091003</t>
+          <t>191306005</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr">
@@ -5786,17 +5786,17 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin A vasculitis</t>
+          <t>Immunoglobulin G4 related disease</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>191306005</t>
+          <t>10743271000119103</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin A vasculitis</t>
+          <t>Immunoglobulin G4 related disease</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5816,13 +5816,13 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>4101602</t>
+          <t>36717255</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>191306005</t>
+          <t>10743271000119103, 234549008, 722870008</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr">
@@ -5839,17 +5839,17 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin G4 related disease</t>
+          <t>Immunoglobulin G4 related ophthalmic disease</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>10743271000119103</t>
+          <t>1187510006</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin G4 related disease</t>
+          <t>Immunoglobulin G4 related ophthalmic disease</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5869,13 +5869,13 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>36717255</t>
+          <t>37162346</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>10743271000119103, 234549008, 722870008</t>
+          <t>1187510006</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
@@ -5892,17 +5892,17 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin G4 related ophthalmic disease</t>
+          <t>Inclusion body myositis</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>1187510006</t>
+          <t>72315009</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Immunoglobulin G4 related ophthalmic disease</t>
+          <t>Inclusion body myositis</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5922,13 +5922,13 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>37162346</t>
+          <t>4216406</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>1187510006</t>
+          <t>72315009</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr">
@@ -5945,22 +5945,22 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Inclusion body myositis</t>
+          <t>Inflammatory Bowel Disease</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>72315009</t>
+          <t>24526004</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Inclusion body myositis</t>
+          <t>Inflammatory bowel disease</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -5975,13 +5975,13 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>4216406</t>
+          <t>4074815</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>72315009</t>
+          <t>24526004</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
@@ -5998,22 +5998,22 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Inflammatory Bowel Disease</t>
+          <t>Insulin autoimmune syndrome</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>24526004</t>
+          <t>408539000</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Inflammatory bowel disease</t>
+          <t>Insulin autoimmune syndrome</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -6028,13 +6028,13 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>4074815</t>
+          <t>4252384</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>24526004</t>
+          <t>408539000</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
@@ -6051,17 +6051,17 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Insulin autoimmune syndrome</t>
+          <t>Insulin resistance - type B</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>408539000</t>
+          <t>237652003</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Insulin autoimmune syndrome</t>
+          <t>Insulin resistance - type B</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6081,13 +6081,13 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>4252384</t>
+          <t>4129525</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>408539000</t>
+          <t>237652003</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
@@ -6104,17 +6104,17 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Insulin resistance - type B</t>
+          <t>Intermediate uveitis</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>237652003</t>
+          <t>314429009</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Insulin resistance - type B</t>
+          <t>Intermediate uveitis</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6134,13 +6134,13 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>4129525</t>
+          <t>4197155</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>237652003</t>
+          <t>314429009, 1231232007, 45688009</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr">
@@ -6157,17 +6157,17 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Intermediate uveitis</t>
+          <t>Interstitial lung disease</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>314429009</t>
+          <t>233703007</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Intermediate uveitis</t>
+          <t>Interstitial lung disease</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6187,13 +6187,13 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>4197155</t>
+          <t>4119786</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>314429009, 1231232007, 45688009</t>
+          <t>233703007</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
@@ -6210,17 +6210,17 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Interstitial lung disease</t>
+          <t>Juvenile Rheumatoid Arthritis</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>233703007</t>
+          <t>410502007</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Interstitial lung disease</t>
+          <t>Juvenile idiopathic arthritis</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6235,25 +6235,21 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Juvenile idiopathic arthritis</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>4119786</t>
+          <t>4259507</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>233703007</t>
-        </is>
-      </c>
-      <c r="K117" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>410795001, 239796000</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6263,17 +6259,17 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Juvenile Rheumatoid Arthritis</t>
+          <t>Lichen planus</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>410502007</t>
+          <t>4776004</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Juvenile idiopathic arthritis</t>
+          <t>Lichen planus</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6288,21 +6284,25 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>Juvenile idiopathic arthritis</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>4259507</t>
+          <t>132703</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>410795001, 239796000</t>
-        </is>
-      </c>
-      <c r="K118" s="2" t="inlineStr"/>
+          <t>4776004</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -6312,17 +6312,17 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Lichen planus</t>
+          <t>Lichen sclerosus</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>4776004</t>
+          <t>895454001</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Lichen planus</t>
+          <t>Lichen sclerosus</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6342,13 +6342,13 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>132703</t>
+          <t>619430</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>4776004</t>
+          <t>895454001, 25674000</t>
         </is>
       </c>
       <c r="K119" s="5" t="inlineStr">
@@ -6365,17 +6365,17 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Lichen sclerosus</t>
+          <t>Ligneous conjunctivitis</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>895454001</t>
+          <t>403435005</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Lichen sclerosus</t>
+          <t>Ligneous conjunctivitis</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6395,13 +6395,13 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>619430</t>
+          <t>4296491</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>895454001, 25674000</t>
+          <t>403435005</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr">
@@ -6418,17 +6418,17 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Ligneous conjunctivitis</t>
+          <t>Limbic encephalitis</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>403435005</t>
+          <t>230192003</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Ligneous conjunctivitis</t>
+          <t>Limbic encephalitis</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6448,13 +6448,13 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>4296491</t>
+          <t>4041673</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>403435005</t>
+          <t>230192003</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr">
@@ -6471,17 +6471,17 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis</t>
+          <t>Limbic encephalitis with dipeptidyl-peptidase 6 antibodies</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>230192003</t>
+          <t>773395008</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis</t>
+          <t>Limbic encephalitis with dipeptidyl-peptidase 6 antibodies</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6501,13 +6501,13 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>4041673</t>
+          <t>36676495</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>230192003</t>
+          <t>773395008</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
@@ -6524,17 +6524,17 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis with dipeptidyl-peptidase 6 antibodies</t>
+          <t>Limbic encephalitis with leucine-rich glioma-inactivated 1 antibodies</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>773395008</t>
+          <t>763794005</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis with dipeptidyl-peptidase 6 antibodies</t>
+          <t>Limbic encephalitis with leucine-rich glioma-inactivated 1 antibodies</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6554,13 +6554,13 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>36676495</t>
+          <t>35607961</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>773395008</t>
+          <t>763794005</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
@@ -6577,17 +6577,17 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis with leucine-rich glioma-inactivated 1 antibodies</t>
+          <t>Linear IgA dermatosis</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>763794005</t>
+          <t>95330001</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Limbic encephalitis with leucine-rich glioma-inactivated 1 antibodies</t>
+          <t>Linear IgA dermatosis</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6607,13 +6607,13 @@
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>35607961</t>
+          <t>4317262</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>763794005</t>
+          <t>95330001</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
@@ -6630,17 +6630,17 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Linear IgA dermatosis</t>
+          <t>Lipomatosis dolorosa</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>95330001</t>
+          <t>71404003</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Linear IgA dermatosis</t>
+          <t>Lipomatosis dolorosa</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6660,13 +6660,13 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>4317262</t>
+          <t>4324974</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>95330001</t>
+          <t>71404003</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr">
@@ -6683,17 +6683,17 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Lipomatosis dolorosa</t>
+          <t>Lupus vasculitis</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>71404003</t>
+          <t>239944008</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Lipomatosis dolorosa</t>
+          <t>Lupus vasculitis</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6713,13 +6713,13 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>4324974</t>
+          <t>4344495</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>71404003</t>
+          <t>239944008</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
@@ -6736,50 +6736,26 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Lupus vasculitis</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>239944008</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>Lupus vasculitis</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Male infertility associated with antisperm antibodies</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr"/>
+      <c r="D127" s="3" t="inlineStr"/>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H127" s="4" t="inlineStr">
-        <is>
-          <t>4344495</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr"/>
       <c r="I127" s="2" t="inlineStr"/>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>239944008</t>
-        </is>
-      </c>
-      <c r="K127" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>414643008</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -6789,26 +6765,50 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Male infertility associated with antisperm antibodies</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr"/>
-      <c r="D128" s="3" t="inlineStr"/>
-      <c r="E128" s="2" t="inlineStr"/>
-      <c r="F128" s="2" t="inlineStr"/>
+          <t>Microscopic colitis</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>235753003</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Microscopic colitis</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>4340799</t>
+        </is>
+      </c>
       <c r="I128" s="2" t="inlineStr"/>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>414643008</t>
-        </is>
-      </c>
-      <c r="K128" s="2" t="inlineStr"/>
+          <t>235753003</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -6818,17 +6818,17 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Microscopic colitis</t>
+          <t>Microscopic polyangiitis</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>235753003</t>
+          <t>1144805008</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Microscopic colitis</t>
+          <t>Microscopic polyangiitis</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6848,13 +6848,13 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>4340799</t>
+          <t>606328</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>235753003</t>
+          <t>1144805008</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr">
@@ -6871,17 +6871,17 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Microscopic polyangiitis</t>
+          <t>Mixed collagen vascular disease</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>1144805008</t>
+          <t>398049005</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Microscopic polyangiitis</t>
+          <t>Mixed collagen vascular disease</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6901,13 +6901,13 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>606328</t>
+          <t>4134867</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>1144805008</t>
+          <t>398049005</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr">
@@ -6924,17 +6924,17 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Mixed collagen vascular disease</t>
+          <t>Mooren's ulcer</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>398049005</t>
+          <t>22440001</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Mixed collagen vascular disease</t>
+          <t>Mooren's ulcer</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -6954,13 +6954,13 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>4134867</t>
+          <t>435271</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>398049005</t>
+          <t>22440001</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr">
@@ -6977,17 +6977,17 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Mooren's ulcer</t>
+          <t>Morphea</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>22440001</t>
+          <t>201049004</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Mooren's ulcer</t>
+          <t>Morphea</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7007,13 +7007,13 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>435271</t>
+          <t>4066845</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>22440001</t>
+          <t>201048007, 201049004</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
@@ -7030,17 +7030,17 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Morphea</t>
+          <t>Motor neuropathy with multiple conduction block</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>201049004</t>
+          <t>230591002</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Morphea</t>
+          <t>Motor neuropathy with multiple conduction block</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7060,13 +7060,13 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>4066845</t>
+          <t>4046338</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>201048007, 201049004</t>
+          <t>230591002</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr">
@@ -7083,17 +7083,17 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Motor neuropathy with multiple conduction block</t>
+          <t>Moyamoya disease</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>230591002</t>
+          <t>69116000</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Motor neuropathy with multiple conduction block</t>
+          <t>Moyamoya disease</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7113,13 +7113,13 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>4046338</t>
+          <t>378774</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>230591002</t>
+          <t>69116000</t>
         </is>
       </c>
       <c r="K134" s="5" t="inlineStr">
@@ -7136,17 +7136,17 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Moyamoya disease</t>
+          <t>Multiple sclerosis</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>69116000</t>
+          <t>24700007</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Moyamoya disease</t>
+          <t>Multiple sclerosis</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7166,13 +7166,13 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>378774</t>
+          <t>374919</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>69116000</t>
+          <t>24700007, 428700003, 426373005, 49692006, 128460000</t>
         </is>
       </c>
       <c r="K135" s="5" t="inlineStr">
@@ -7189,17 +7189,17 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Multiple sclerosis</t>
+          <t>Myasthenia gravis</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>24700007</t>
+          <t>91637004</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Multiple sclerosis</t>
+          <t>Myasthenia gravis</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7219,13 +7219,13 @@
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>374919</t>
+          <t>76685</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>24700007, 428700003, 426373005, 49692006, 128460000</t>
+          <t>91637004</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr">
@@ -7242,17 +7242,17 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Myasthenia gravis</t>
+          <t>Myelin oligodendrocyte glycoprotein antibody-associated disease</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>91637004</t>
+          <t>1237194006</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Myasthenia gravis</t>
+          <t>Myelin oligodendrocyte glycoprotein antibody-associated disease</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7272,13 +7272,13 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>76685</t>
+          <t>37164973</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr"/>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>91637004</t>
+          <t>1237194006, 718213001</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
@@ -7295,17 +7295,17 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Myelin oligodendrocyte glycoprotein antibody-associated disease</t>
+          <t>Myocarditis due to autoimmune disease</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>1237194006</t>
+          <t>871640001</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Myelin oligodendrocyte glycoprotein antibody-associated disease</t>
+          <t>Myocarditis due to autoimmune disease</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7325,13 +7325,13 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>37164973</t>
+          <t>3656114</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>1237194006, 718213001</t>
+          <t>871640001, 37217002</t>
         </is>
       </c>
       <c r="K138" s="5" t="inlineStr">
@@ -7348,17 +7348,17 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Myocarditis due to autoimmune disease</t>
+          <t>Myositis</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>871640001</t>
+          <t>26889001</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Myocarditis due to autoimmune disease</t>
+          <t>Myositis</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7378,13 +7378,13 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>3656114</t>
+          <t>73001</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>871640001, 37217002</t>
+          <t>722991004, 715863001, 702380008, 26889001</t>
         </is>
       </c>
       <c r="K139" s="5" t="inlineStr">
@@ -7401,17 +7401,17 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Myositis</t>
+          <t>Necrotizing vasculitis</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>26889001</t>
+          <t>11791001</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Myositis</t>
+          <t>Necrotizing vasculitis</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7431,13 +7431,13 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>4039691</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>722991004, 715863001, 702380008, 26889001</t>
+          <t>11791001</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Necrotizing vasculitis</t>
+          <t>Neonatal lupus erythematosus</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>11791001</t>
+          <t>95609003</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Necrotizing vasculitis</t>
+          <t>Neonatal lupus erythematosus</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7484,13 +7484,13 @@
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>4039691</t>
+          <t>4316373</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>11791001</t>
+          <t>95609003</t>
         </is>
       </c>
       <c r="K141" s="5" t="inlineStr">
@@ -7507,17 +7507,17 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Neonatal lupus erythematosus</t>
+          <t>Neuralgic amyotrophy</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>95609003</t>
+          <t>26609002</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Neonatal lupus erythematosus</t>
+          <t>Neuralgic amyotrophy</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7537,13 +7537,13 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>4316373</t>
+          <t>377271</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>95609003</t>
+          <t>3548001, 26609002</t>
         </is>
       </c>
       <c r="K142" s="5" t="inlineStr">
@@ -7560,17 +7560,17 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Neuralgic amyotrophy</t>
+          <t>Neuromyelitis optica</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>26609002</t>
+          <t>25044007</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Neuralgic amyotrophy</t>
+          <t>Neuromyelitis optica</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7590,13 +7590,13 @@
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>377271</t>
+          <t>380995</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>3548001, 26609002</t>
+          <t>25044007</t>
         </is>
       </c>
       <c r="K143" s="5" t="inlineStr">
@@ -7613,17 +7613,17 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Neuromyelitis optica</t>
+          <t>Neuromyotonia</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>25044007</t>
+          <t>305719002</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Neuromyelitis optica</t>
+          <t>Neuromyotonia</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7643,13 +7643,13 @@
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>380995</t>
+          <t>4125693</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>25044007</t>
+          <t>305719002</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr">
@@ -7666,50 +7666,26 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Neuromyotonia</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>305719002</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>Neuromyotonia</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Ocular myasthenia gravis</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr"/>
+      <c r="D145" s="3" t="inlineStr"/>
+      <c r="E145" s="2" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H145" s="4" t="inlineStr">
-        <is>
-          <t>4125693</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr"/>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>305719002</t>
-        </is>
-      </c>
-      <c r="K145" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>230684008</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -7719,26 +7695,50 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Ocular myasthenia gravis</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr"/>
-      <c r="D146" s="3" t="inlineStr"/>
-      <c r="E146" s="2" t="inlineStr"/>
-      <c r="F146" s="2" t="inlineStr"/>
+          <t>Ophthalmoplegia due to Graves' disease</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>104461000119104</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Ophthalmoplegia due to Graves' disease</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>45757069</t>
+        </is>
+      </c>
       <c r="I146" s="2" t="inlineStr"/>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>230684008</t>
-        </is>
-      </c>
-      <c r="K146" s="2" t="inlineStr"/>
+          <t>104461000119104, 276177000</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -7748,17 +7748,17 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Ophthalmoplegia due to Graves' disease</t>
+          <t>Opsoclonus-myoclonus syndrome</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>104461000119104</t>
+          <t>230350000</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Ophthalmoplegia due to Graves' disease</t>
+          <t>Opsoclonus-myoclonus syndrome</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -7778,13 +7778,13 @@
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>45757069</t>
+          <t>4043399</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr"/>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>104461000119104, 276177000</t>
+          <t>230350000</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
@@ -7801,17 +7801,17 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Opsoclonus-myoclonus syndrome</t>
+          <t>Palindromic rheumatism</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>230350000</t>
+          <t>50442003</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Opsoclonus-myoclonus syndrome</t>
+          <t>Palindromic rheumatism</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -7831,13 +7831,13 @@
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>4043399</t>
+          <t>76196</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>230350000</t>
+          <t>50442003</t>
         </is>
       </c>
       <c r="K148" s="5" t="inlineStr">
@@ -7854,17 +7854,17 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Palindromic rheumatism</t>
+          <t>Paraneoplastic cerebellar degeneration</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>50442003</t>
+          <t>192877007</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Palindromic rheumatism</t>
+          <t>Paraneoplastic cerebellar degeneration</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -7884,13 +7884,13 @@
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>76196</t>
+          <t>4102330</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>50442003</t>
+          <t>192877007</t>
         </is>
       </c>
       <c r="K149" s="5" t="inlineStr">
@@ -7907,50 +7907,22 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Paraneoplastic cerebellar degeneration</t>
-        </is>
-      </c>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>192877007</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>Paraneoplastic cerebellar degeneration</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Paraneoplastic pemphigus</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr"/>
+      <c r="D150" s="3" t="inlineStr"/>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>4102330</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr"/>
       <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>192877007</t>
-        </is>
-      </c>
-      <c r="K150" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J150" s="3" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -7960,22 +7932,50 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Paraneoplastic pemphigus</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr"/>
-      <c r="D151" s="3" t="inlineStr"/>
-      <c r="E151" s="2" t="inlineStr"/>
-      <c r="F151" s="2" t="inlineStr"/>
+          <t>Paroxysmal cold hemoglobinuria</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>127057004</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Paroxysmal cold hemoglobinuria</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>4131917</t>
+        </is>
+      </c>
       <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="3" t="inlineStr"/>
-      <c r="K151" s="2" t="inlineStr"/>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>127057004</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -7985,17 +7985,17 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Paroxysmal cold hemoglobinuria</t>
+          <t>Paroxysmal nocturnal hemoglobinuria</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>127057004</t>
+          <t>1963002</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Paroxysmal cold hemoglobinuria</t>
+          <t>Paroxysmal nocturnal hemoglobinuria</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8015,13 +8015,13 @@
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>4131917</t>
+          <t>4024671</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr"/>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>127057004</t>
+          <t>1963002</t>
         </is>
       </c>
       <c r="K152" s="5" t="inlineStr">
@@ -8038,17 +8038,17 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Paroxysmal nocturnal hemoglobinuria</t>
+          <t>Pediatric autoimmune neuropsychiatric disorder associated with streptococcal infection</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>1963002</t>
+          <t>446682003</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Paroxysmal nocturnal hemoglobinuria</t>
+          <t>Pediatric autoimmune neuropsychiatric disorder associated with streptococcal infection</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8068,13 +8068,13 @@
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>4024671</t>
+          <t>40488855</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr"/>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>1963002</t>
+          <t>446682003</t>
         </is>
       </c>
       <c r="K153" s="5" t="inlineStr">
@@ -8091,17 +8091,17 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Pediatric autoimmune neuropsychiatric disorder associated with streptococcal infection</t>
+          <t>Pemphigus</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>446682003</t>
+          <t>65172003</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Pediatric autoimmune neuropsychiatric disorder associated with streptococcal infection</t>
+          <t>Pemphigus</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8121,13 +8121,13 @@
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>40488855</t>
+          <t>135338</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr"/>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>446682003</t>
+          <t>46459009, 200907003, 65172003, 36739006, 35154004, 402718003, 49420001</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr">
@@ -8144,17 +8144,17 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Pemphigus</t>
+          <t>POEMS syndrome</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>65172003</t>
+          <t>79268002</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Pemphigus</t>
+          <t>POEMS syndrome</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8174,13 +8174,13 @@
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>135338</t>
+          <t>4193776</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr"/>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>46459009, 200907003, 65172003, 36739006, 35154004, 402718003, 49420001</t>
+          <t>79268002</t>
         </is>
       </c>
       <c r="K155" s="5" t="inlineStr">
@@ -8197,17 +8197,17 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>POEMS syndrome</t>
+          <t>Polyarteritis nodosa</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>79268002</t>
+          <t>155441006</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>POEMS syndrome</t>
+          <t>Polyarteritis nodosa</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8227,13 +8227,13 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>4193776</t>
+          <t>320749</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr"/>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>79268002</t>
+          <t>155441006</t>
         </is>
       </c>
       <c r="K156" s="5" t="inlineStr">
@@ -8250,43 +8250,43 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Polyarteritis nodosa</t>
+          <t>Polyglandular autoimmune syndrome type 1</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>155441006</t>
+          <t>11244009</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Polyarteritis nodosa</t>
+          <t>Polyglandular autoimmune syndrome, type 1</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Autoimmune polyendocrinopathy-candidiasis-ectodermal dystrophy</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>320749</t>
+          <t>4008545</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr"/>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>155441006</t>
+          <t>11244009</t>
         </is>
       </c>
       <c r="K157" s="5" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome type 1</t>
+          <t>Polyglandular autoimmune syndrome type 2</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>11244009</t>
+          <t>403767009</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome, type 1</t>
+          <t>Acrocephalopolysyndactyly type II</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8328,25 +8328,21 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrinopathy-candidiasis-ectodermal dystrophy</t>
+          <t>Carpenter syndrome</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>4008545</t>
+          <t>4301299</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>11244009</t>
-        </is>
-      </c>
-      <c r="K158" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>83728000</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -8356,46 +8352,50 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome type 2</t>
+          <t>Polyglandular autoimmune syndrome type 3</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>403767009</t>
+          <t>449731009</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Acrocephalopolysyndactyly type II</t>
+          <t>Autoimmune polyendocrine syndrome type 3</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>name</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>Carpenter syndrome</t>
+          <t>Autoimmune polyendocrine syndrome type 3</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>4301299</t>
+          <t>42709859</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>83728000</t>
-        </is>
-      </c>
-      <c r="K159" s="2" t="inlineStr"/>
+          <t>449731009</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome type 3</t>
+          <t>Polyglandular autoimmune syndrome type 4</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>449731009</t>
+          <t>449730005</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrine syndrome type 3</t>
+          <t>Autoimmune polyendocrine syndrome type 4</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -8430,18 +8430,18 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrine syndrome type 3</t>
+          <t>Autoimmune polyendocrine syndrome type 4</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>42709859</t>
+          <t>42709858</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr"/>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>449731009</t>
+          <t>449730005</t>
         </is>
       </c>
       <c r="K160" s="5" t="inlineStr">
@@ -8458,17 +8458,17 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Polyglandular autoimmune syndrome type 4</t>
+          <t>Polymyalgia rheumatica</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>449730005</t>
+          <t>65323003</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrine syndrome type 4</t>
+          <t>Polymyalgia rheumatica</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8483,18 +8483,18 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune polyendocrine syndrome type 4</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>42709858</t>
+          <t>255348</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr"/>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>449730005</t>
+          <t>65323003</t>
         </is>
       </c>
       <c r="K161" s="5" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Polymyalgia rheumatica</t>
+          <t>Polymyositis</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>65323003</t>
+          <t>31384009</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Polymyalgia rheumatica</t>
+          <t>Polymyositis</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8541,13 +8541,13 @@
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>255348</t>
+          <t>80800</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr"/>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>65323003</t>
+          <t>31384009</t>
         </is>
       </c>
       <c r="K162" s="5" t="inlineStr">
@@ -8564,17 +8564,17 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Polymyositis</t>
+          <t>Postmyocardial infarction syndrome</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>31384009</t>
+          <t>1258984009</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Polymyositis</t>
+          <t>Post-cardiac injury syndrome</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8589,25 +8589,21 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Post-cardiac injury syndrome</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>80800</t>
+          <t>37166030</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr"/>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>31384009</t>
-        </is>
-      </c>
-      <c r="K163" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>827164008, 66189004, 58600007, 278536002</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -8617,17 +8613,17 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Postmyocardial infarction syndrome</t>
+          <t>Postural orthostatic tachycardia syndrome</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>1258984009</t>
+          <t>371073003</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Post-cardiac injury syndrome</t>
+          <t>Postural orthostatic tachycardia syndrome</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8642,21 +8638,25 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>Post-cardiac injury syndrome</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>37166030</t>
+          <t>4159659</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr"/>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>827164008, 66189004, 58600007, 278536002</t>
-        </is>
-      </c>
-      <c r="K164" s="2" t="inlineStr"/>
+          <t>371073003</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -8666,17 +8666,17 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Postural orthostatic tachycardia syndrome</t>
+          <t>Primary acquired chylomicronemia</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>371073003</t>
+          <t>402475008</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Postural orthostatic tachycardia syndrome</t>
+          <t>Primary acquired chylomicronemia</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -8696,13 +8696,13 @@
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>4159659</t>
+          <t>4223495</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr"/>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>371073003</t>
+          <t>402475008</t>
         </is>
       </c>
       <c r="K165" s="5" t="inlineStr">
@@ -8719,17 +8719,17 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Primary acquired chylomicronemia</t>
+          <t>Primary biliary cholangitis</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>402475008</t>
+          <t>31712002</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Primary acquired chylomicronemia</t>
+          <t>Primary biliary cholangitis</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -8749,13 +8749,13 @@
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>4223495</t>
+          <t>4135822</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>402475008</t>
+          <t>31712002</t>
         </is>
       </c>
       <c r="K166" s="5" t="inlineStr">
@@ -8772,17 +8772,17 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Primary biliary cholangitis</t>
+          <t>Primary idiopathic dilated cardiomyopathy</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>31712002</t>
+          <t>53043001</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Primary biliary cholangitis</t>
+          <t>Primary idiopathic dilated cardiomyopathy</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -8802,13 +8802,13 @@
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>4135822</t>
+          <t>4203149</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr"/>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>31712002</t>
+          <t>53043001</t>
         </is>
       </c>
       <c r="K167" s="5" t="inlineStr">
@@ -8825,50 +8825,26 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Primary idiopathic dilated cardiomyopathy</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>53043001</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>Primary idiopathic dilated cardiomyopathy</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Primary immune deficiency</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr"/>
+      <c r="D168" s="3" t="inlineStr"/>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>4203149</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr"/>
       <c r="I168" s="2" t="inlineStr"/>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>53043001</t>
-        </is>
-      </c>
-      <c r="K168" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>442459007, 362993009, 36138009, 31323000, 37548006</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -8878,26 +8854,50 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Primary immune deficiency</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr"/>
-      <c r="D169" s="3" t="inlineStr"/>
-      <c r="E169" s="2" t="inlineStr"/>
-      <c r="F169" s="2" t="inlineStr"/>
+          <t>Primary sclerosing cholangitis</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>197441003</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Primary sclerosing cholangitis</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>4058821</t>
+        </is>
+      </c>
       <c r="I169" s="2" t="inlineStr"/>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>442459007, 362993009, 36138009, 31323000, 37548006</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr"/>
+          <t>197441003</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -8907,17 +8907,17 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Primary sclerosing cholangitis</t>
+          <t>Progressive hemifacial atrophy</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>197441003</t>
+          <t>718224004</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Primary sclerosing cholangitis</t>
+          <t>Progressive hemifacial atrophy</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -8937,13 +8937,13 @@
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>4058821</t>
+          <t>37397558</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr"/>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>197441003</t>
+          <t>718224004</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr">
@@ -8960,17 +8960,17 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Progressive hemifacial atrophy</t>
+          <t>Psoriasis</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>718224004</t>
+          <t>9014002</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Progressive hemifacial atrophy</t>
+          <t>Psoriasis</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -8990,13 +8990,13 @@
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>37397558</t>
+          <t>140168</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr"/>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>718224004</t>
+          <t>37042000, 9014002</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
@@ -9013,17 +9013,17 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Psoriasis</t>
+          <t>Psoriatic arthritis</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>9014002</t>
+          <t>156370009</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Psoriasis</t>
+          <t>Psoriatic arthritis</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9043,13 +9043,13 @@
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>140168</t>
+          <t>40319772</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>37042000, 9014002</t>
+          <t>156370009, 33339001</t>
         </is>
       </c>
       <c r="K172" s="5" t="inlineStr">
@@ -9066,17 +9066,17 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Psoriatic arthritis</t>
+          <t>Pure red cell aplasia</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>156370009</t>
+          <t>50715003</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Psoriatic arthritis</t>
+          <t>Pure red cell aplasia</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9096,13 +9096,13 @@
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>40319772</t>
+          <t>140065</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr"/>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>156370009, 33339001</t>
+          <t>50715003</t>
         </is>
       </c>
       <c r="K173" s="5" t="inlineStr">
@@ -9119,17 +9119,17 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Pure red cell aplasia</t>
+          <t>Pyoderma gangrenosum</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>50715003</t>
+          <t>74578003</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Pure red cell aplasia</t>
+          <t>Pyoderma gangrenosum</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9149,13 +9149,13 @@
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>140065</t>
+          <t>133283</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr"/>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>50715003</t>
+          <t>74578003</t>
         </is>
       </c>
       <c r="K174" s="5" t="inlineStr">
@@ -9172,17 +9172,17 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Pyoderma gangrenosum</t>
+          <t>Rasmussen syndrome</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>74578003</t>
+          <t>230191005</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Pyoderma gangrenosum</t>
+          <t>Rasmussen syndrome</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9202,13 +9202,13 @@
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>133283</t>
+          <t>4041672</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr"/>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>74578003</t>
+          <t>230191005, 435341000124104</t>
         </is>
       </c>
       <c r="K175" s="5" t="inlineStr">
@@ -9225,17 +9225,17 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Rasmussen syndrome</t>
+          <t>Secondary Raynaud's phenomenon</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>230191005</t>
+          <t>356198000</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Rasmussen syndrome</t>
+          <t>Secondary Raynaud's phenomenon</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9255,13 +9255,13 @@
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>4041672</t>
+          <t>4229162</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr"/>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>230191005, 435341000124104</t>
+          <t>356198000, 266261006</t>
         </is>
       </c>
       <c r="K176" s="5" t="inlineStr">
@@ -9278,17 +9278,17 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Secondary Raynaud's phenomenon</t>
+          <t>Reactive arthritis</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>356198000</t>
+          <t>201736002</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Secondary Raynaud's phenomenon</t>
+          <t>Reactive arthritis</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9308,13 +9308,13 @@
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>4229162</t>
+          <t>40399768</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr"/>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>356198000, 266261006</t>
+          <t>201736002, 67224007</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
@@ -9331,17 +9331,17 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Reactive arthritis</t>
+          <t>Relapsing polychondritis</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>201736002</t>
+          <t>72275000</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Reactive arthritis</t>
+          <t>Relapsing polychondritis</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9361,13 +9361,13 @@
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>40399768</t>
+          <t>4216873</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>201736002, 67224007</t>
+          <t>72275000</t>
         </is>
       </c>
       <c r="K178" s="5" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Relapsing polychondritis</t>
+          <t>Restless legs</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>72275000</t>
+          <t>32914008</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Relapsing polychondritis</t>
+          <t>Restless legs</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9414,13 +9414,13 @@
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>4216873</t>
+          <t>73754</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr"/>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>72275000</t>
+          <t>32914008</t>
         </is>
       </c>
       <c r="K179" s="5" t="inlineStr">
@@ -9437,17 +9437,17 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Restless legs</t>
+          <t>Retinocochleocerebral vasculopathy</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>32914008</t>
+          <t>702575003</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Restless legs</t>
+          <t>Retinocochleocerebral vasculopathy</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -9467,13 +9467,13 @@
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>73754</t>
+          <t>45765600</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr"/>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>32914008</t>
+          <t>702575003</t>
         </is>
       </c>
       <c r="K180" s="5" t="inlineStr">
@@ -9490,22 +9490,22 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Retinocochleocerebral vasculopathy</t>
+          <t>Rheumatic Chorea</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>702575003</t>
+          <t>46826000</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>Retinocochleocerebral vasculopathy</t>
+          <t>Rheumatic chorea</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
@@ -9520,13 +9520,13 @@
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>45765600</t>
+          <t>444120</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr"/>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>702575003</t>
+          <t>46826000</t>
         </is>
       </c>
       <c r="K181" s="5" t="inlineStr">
@@ -9543,22 +9543,22 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic Chorea</t>
+          <t>Rheumatic fever</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>46826000</t>
+          <t>58718002</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic chorea</t>
+          <t>Rheumatic fever</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -9573,13 +9573,13 @@
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
-          <t>444120</t>
+          <t>442313</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr"/>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>46826000</t>
+          <t>58718002, 194709000</t>
         </is>
       </c>
       <c r="K182" s="5" t="inlineStr">
@@ -9596,17 +9596,17 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic fever</t>
+          <t>Rheumatoid aortitis</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>58718002</t>
+          <t>38877003</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic fever</t>
+          <t>Rheumatoid aortitis</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9626,13 +9626,13 @@
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>442313</t>
+          <t>4306357</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr"/>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>58718002, 194709000</t>
+          <t>38877003</t>
         </is>
       </c>
       <c r="K183" s="5" t="inlineStr">
@@ -9649,17 +9649,17 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid aortitis</t>
+          <t>Rheumatoid arthritis</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>38877003</t>
+          <t>69896004</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid aortitis</t>
+          <t>Rheumatoid arthritis</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -9679,13 +9679,13 @@
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
-          <t>4306357</t>
+          <t>80809</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr"/>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>38877003</t>
+          <t>69896004</t>
         </is>
       </c>
       <c r="K184" s="5" t="inlineStr">
@@ -9702,17 +9702,17 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid arthritis</t>
+          <t>Rheumatoid vasculitis</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>69896004</t>
+          <t>400054000</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid arthritis</t>
+          <t>Rheumatoid vasculitis</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -9732,13 +9732,13 @@
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>80809</t>
+          <t>4271003</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr"/>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>69896004</t>
+          <t>400054000</t>
         </is>
       </c>
       <c r="K185" s="5" t="inlineStr">
@@ -9755,17 +9755,17 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid vasculitis</t>
+          <t>Sarcoidosis</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>400054000</t>
+          <t>31541009</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid vasculitis</t>
+          <t>Sarcoidosis</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -9785,13 +9785,13 @@
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>4271003</t>
+          <t>438688</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr"/>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>400054000</t>
+          <t>72470008, 238676008, 31541009</t>
         </is>
       </c>
       <c r="K186" s="5" t="inlineStr">
@@ -9808,17 +9808,17 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Sarcoidosis</t>
+          <t>Schnitzler syndrome</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>31541009</t>
+          <t>402415001</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Sarcoidosis</t>
+          <t>Schnitzler syndrome</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -9838,13 +9838,13 @@
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t>438688</t>
+          <t>4297647</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr"/>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>72470008, 238676008, 31541009</t>
+          <t>402415001</t>
         </is>
       </c>
       <c r="K187" s="5" t="inlineStr">
@@ -9861,17 +9861,17 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Schnitzler syndrome</t>
+          <t>Scleritis</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>402415001</t>
+          <t>78370002</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Schnitzler syndrome</t>
+          <t>Scleritis</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -9891,13 +9891,13 @@
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
-          <t>4297647</t>
+          <t>434944</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr"/>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>402415001</t>
+          <t>78370002</t>
         </is>
       </c>
       <c r="K188" s="5" t="inlineStr">
@@ -9914,17 +9914,17 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Scleritis</t>
+          <t>Sjögren's disease</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>78370002</t>
+          <t>302896008</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Scleritis</t>
+          <t>Keratoconjunctivitis sicca</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -9939,25 +9939,21 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Keratoconjunctivitis sicca</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>434944</t>
+          <t>4120320</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr"/>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>78370002</t>
-        </is>
-      </c>
-      <c r="K189" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>83901003</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -9967,17 +9963,17 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Sjögren's disease</t>
+          <t>SLE glomerulonephritis syndrome</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>302896008</t>
+          <t>68815009</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Keratoconjunctivitis sicca</t>
+          <t>SLE glomerulonephritis syndrome</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -9992,21 +9988,25 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>Keratoconjunctivitis sicca</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
-          <t>4120320</t>
+          <t>4285717</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr"/>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>83901003</t>
-        </is>
-      </c>
-      <c r="K190" s="2" t="inlineStr"/>
+          <t>68815009</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -10016,17 +10016,17 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>SLE glomerulonephritis syndrome</t>
+          <t>Small fiber neuropathy</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>68815009</t>
+          <t>709489006</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>SLE glomerulonephritis syndrome</t>
+          <t>Small fiber neuropathy</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10046,13 +10046,13 @@
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>4285717</t>
+          <t>46271378</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr"/>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>68815009</t>
+          <t>709489006</t>
         </is>
       </c>
       <c r="K191" s="5" t="inlineStr">
@@ -10069,17 +10069,17 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Small fiber neuropathy</t>
+          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>709489006</t>
+          <t>771271000</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Small fiber neuropathy</t>
+          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10099,13 +10099,13 @@
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
-          <t>46271378</t>
+          <t>36674282</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr"/>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>709489006</t>
+          <t>771271000</t>
         </is>
       </c>
       <c r="K192" s="5" t="inlineStr">
@@ -10122,17 +10122,17 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
+          <t>Stiff-person syndrome</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>771271000</t>
+          <t>5217008</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
+          <t>Stiff-person syndrome</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10152,13 +10152,13 @@
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>36674282</t>
+          <t>379008</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr"/>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>771271000</t>
+          <t>5217008</t>
         </is>
       </c>
       <c r="K193" s="5" t="inlineStr">
@@ -10175,17 +10175,17 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Stiff-person syndrome</t>
+          <t>Subacute bacterial endocarditis</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>5217008</t>
+          <t>73774007</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Stiff-person syndrome</t>
+          <t>Subacute bacterial endocarditis</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10205,13 +10205,13 @@
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
-          <t>379008</t>
+          <t>4249899</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr"/>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>5217008</t>
+          <t>73774007</t>
         </is>
       </c>
       <c r="K194" s="5" t="inlineStr">
@@ -10228,17 +10228,17 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Subacute bacterial endocarditis</t>
+          <t>Sympathetic uveitis</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>73774007</t>
+          <t>75315001</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>Subacute bacterial endocarditis</t>
+          <t>Sympathetic uveitis</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10258,13 +10258,13 @@
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t>4249899</t>
+          <t>438739</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr"/>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>73774007</t>
+          <t>75315001</t>
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr">
@@ -10281,17 +10281,17 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Sympathetic uveitis</t>
+          <t>Systemic lupus erythematosus</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>75315001</t>
+          <t>55464009</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Sympathetic uveitis</t>
+          <t>Systemic lupus erythematosus</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10311,13 +10311,13 @@
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
-          <t>438739</t>
+          <t>257628</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>75315001</t>
+          <t>55464009</t>
         </is>
       </c>
       <c r="K196" s="5" t="inlineStr">
@@ -10334,17 +10334,17 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Systemic lupus erythematosus</t>
+          <t>Systemic mast cell disease</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>55464009</t>
+          <t>397016004</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Systemic lupus erythematosus</t>
+          <t>Systemic mast cell disease</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10364,13 +10364,13 @@
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>257628</t>
+          <t>4246284</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr"/>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>55464009</t>
+          <t>397016004</t>
         </is>
       </c>
       <c r="K197" s="5" t="inlineStr">
@@ -10387,17 +10387,17 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Systemic mast cell disease</t>
+          <t>Systemic sclerosis</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>397016004</t>
+          <t>89155008</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Systemic mast cell disease</t>
+          <t>Systemic sclerosis</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10417,13 +10417,13 @@
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>4246284</t>
+          <t>134442</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr"/>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>397016004</t>
+          <t>89155008</t>
         </is>
       </c>
       <c r="K198" s="5" t="inlineStr">
@@ -10440,17 +10440,17 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis</t>
+          <t>Systemic sclerosis with limited cutaneous involvement</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>89155008</t>
+          <t>298285004</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis</t>
+          <t>Systemic sclerosis with limited cutaneous involvement</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10470,13 +10470,13 @@
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
-          <t>134442</t>
+          <t>4185187</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr"/>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>89155008</t>
+          <t>298285004, 31848007, 128461001</t>
         </is>
       </c>
       <c r="K199" s="5" t="inlineStr">
@@ -10493,17 +10493,17 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis with limited cutaneous involvement</t>
+          <t>Takayasu's arteritis</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>298285004</t>
+          <t>359789008</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis with limited cutaneous involvement</t>
+          <t>Takayasu's disease</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10518,18 +10518,18 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Takayasu's disease</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t>4185187</t>
+          <t>440740</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr"/>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>298285004, 31848007, 128461001</t>
+          <t>359789008</t>
         </is>
       </c>
       <c r="K200" s="5" t="inlineStr">
@@ -10546,17 +10546,17 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Takayasu's arteritis</t>
+          <t>Temporal arteritis</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>359789008</t>
+          <t>400130008</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Takayasu's disease</t>
+          <t>Temporal arteritis</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -10571,18 +10571,18 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>Takayasu's disease</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
-          <t>440740</t>
+          <t>4290976</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr"/>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>359789008</t>
+          <t>400130008</t>
         </is>
       </c>
       <c r="K201" s="5" t="inlineStr">
@@ -10599,50 +10599,22 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Temporal arteritis</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="inlineStr">
-        <is>
-          <t>400130008</t>
-        </is>
-      </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>Temporal arteritis</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>TIF1-gamma positive dermatomyositis</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr"/>
+      <c r="D202" s="3" t="inlineStr"/>
+      <c r="E202" s="2" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H202" s="4" t="inlineStr">
-        <is>
-          <t>4290976</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr"/>
       <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="3" t="inlineStr">
-        <is>
-          <t>400130008</t>
-        </is>
-      </c>
-      <c r="K202" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J202" s="3" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -10652,22 +10624,50 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>TIF1-gamma positive dermatomyositis</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr"/>
-      <c r="D203" s="3" t="inlineStr"/>
-      <c r="E203" s="2" t="inlineStr"/>
-      <c r="F203" s="2" t="inlineStr"/>
+          <t>Tolosa-Hunt syndrome</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>95794005</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>Tolosa-Hunt syndrome</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H203" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H203" s="4" t="inlineStr">
+        <is>
+          <t>4317989</t>
+        </is>
+      </c>
       <c r="I203" s="2" t="inlineStr"/>
-      <c r="J203" s="3" t="inlineStr"/>
-      <c r="K203" s="2" t="inlineStr"/>
+      <c r="J203" s="3" t="inlineStr">
+        <is>
+          <t>95794005</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -10677,27 +10677,27 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Tolosa-Hunt syndrome</t>
+          <t>Transverse myelitis</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>95794005</t>
+          <t>16631009</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Tolosa-Hunt syndrome</t>
+          <t>Transverse myelopathy syndrome</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -10707,13 +10707,13 @@
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>4317989</t>
+          <t>443904</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>95794005</t>
+          <t>16631009</t>
         </is>
       </c>
       <c r="K204" s="5" t="inlineStr">
@@ -10730,27 +10730,27 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Transverse myelitis</t>
+          <t>Ulcerative colitis</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>16631009</t>
+          <t>64766004</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Transverse myelopathy syndrome</t>
+          <t>Ulcerative colitis</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>name</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -10760,13 +10760,13 @@
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t>443904</t>
+          <t>81893</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr"/>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>16631009</t>
+          <t>64766004</t>
         </is>
       </c>
       <c r="K205" s="5" t="inlineStr">
@@ -10783,17 +10783,17 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Ulcerative colitis</t>
+          <t>Undifferentiated connective tissue disease</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>64766004</t>
+          <t>239918008</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Ulcerative colitis</t>
+          <t>Undifferentiated connective tissue disease</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -10813,13 +10813,13 @@
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
-          <t>81893</t>
+          <t>4344165</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr"/>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>64766004</t>
+          <t>239918008</t>
         </is>
       </c>
       <c r="K206" s="5" t="inlineStr">
@@ -10836,50 +10836,26 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>Undifferentiated connective tissue disease</t>
-        </is>
-      </c>
-      <c r="C207" s="4" t="inlineStr">
-        <is>
-          <t>239918008</t>
-        </is>
-      </c>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>Undifferentiated connective tissue disease</t>
-        </is>
-      </c>
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F207" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Urticarial vasculitis</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr"/>
+      <c r="D207" s="3" t="inlineStr"/>
+      <c r="E207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H207" s="4" t="inlineStr">
-        <is>
-          <t>4344165</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr"/>
       <c r="I207" s="2" t="inlineStr"/>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>239918008</t>
-        </is>
-      </c>
-      <c r="K207" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>402656007</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -10889,26 +10865,50 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Urticarial vasculitis</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr"/>
-      <c r="D208" s="3" t="inlineStr"/>
-      <c r="E208" s="2" t="inlineStr"/>
-      <c r="F208" s="2" t="inlineStr"/>
+          <t>Uveitis</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>128473001</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Uveitis</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H208" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t>4028363</t>
+        </is>
+      </c>
       <c r="I208" s="2" t="inlineStr"/>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>402656007</t>
-        </is>
-      </c>
-      <c r="K208" s="2" t="inlineStr"/>
+          <t>128473001, 231947004</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -10918,17 +10918,17 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Uveitis</t>
+          <t>Vitiligo</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>128473001</t>
+          <t>56727007</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Uveitis</t>
+          <t>Vitiligo</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -10948,13 +10948,13 @@
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>4028363</t>
+          <t>138502</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr"/>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>128473001, 231947004</t>
+          <t>56727007</t>
         </is>
       </c>
       <c r="K209" s="5" t="inlineStr">
@@ -10971,17 +10971,17 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Vitiligo</t>
+          <t>Vogt-Koyanagi-Harada disease</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>56727007</t>
+          <t>193497004</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Vitiligo</t>
+          <t>Vogt-Koyanagi-Harada disease</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11001,13 +11001,13 @@
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
-          <t>138502</t>
+          <t>4108968</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr"/>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>56727007</t>
+          <t>193497004</t>
         </is>
       </c>
       <c r="K210" s="5" t="inlineStr">
@@ -11024,17 +11024,17 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Vogt-Koyanagi-Harada disease</t>
+          <t>Warm autoimmune hemolytic anemia</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>193497004</t>
+          <t>3978000</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Vogt-Koyanagi-Harada disease</t>
+          <t>Warm autoimmune hemolytic anemia</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -11054,69 +11054,16 @@
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
-          <t>4108968</t>
+          <t>4219853</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr"/>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>193497004</t>
+          <t>3978000</t>
         </is>
       </c>
       <c r="K211" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>ARI:0001211</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="inlineStr">
-        <is>
-          <t>Warm autoimmune hemolytic anemia</t>
-        </is>
-      </c>
-      <c r="C212" s="4" t="inlineStr">
-        <is>
-          <t>3978000</t>
-        </is>
-      </c>
-      <c r="D212" s="3" t="inlineStr">
-        <is>
-          <t>Warm autoimmune hemolytic anemia</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F212" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G212" s="3" t="inlineStr">
-        <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H212" s="4" t="inlineStr">
-        <is>
-          <t>4219853</t>
-        </is>
-      </c>
-      <c r="I212" s="2" t="inlineStr"/>
-      <c r="J212" s="3" t="inlineStr">
-        <is>
-          <t>3978000</t>
-        </is>
-      </c>
-      <c r="K212" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -11181,8 +11128,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId61"/>
@@ -11199,8 +11146,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId79"/>
@@ -11237,20 +11184,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId129"/>
@@ -11261,8 +11208,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId141"/>
@@ -11303,8 +11250,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId181"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId183"/>
@@ -11343,8 +11290,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId217"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId221"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId223"/>
@@ -11377,16 +11324,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId251"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId255"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId256"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId257"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId259"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId263"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId265"/>
@@ -11419,8 +11366,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId293"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId296"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId297"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId298"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId299"/>
@@ -11485,24 +11432,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId358"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId359"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId362"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId363"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId364"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId365"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId366"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId367"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId370"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId371"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId372"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId373"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId374"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId375"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId378"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
